--- a/empleados.xlsx
+++ b/empleados.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Dropbox\NOMINA Y RRHH\NOMINA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\NOMINA Y RRHH\NOMINA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BED8768-C3CC-4B89-9F92-7130CAB743E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FDC354F-F64C-4EC8-B8A6-4CF89E0B3A45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{DA975529-9E83-4FFA-BD35-5CA808A15280}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DA975529-9E83-4FFA-BD35-5CA808A15280}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <si>
     <t>CEDULA</t>
   </si>
@@ -114,9 +125,6 @@
     <t>HERNANDEZ MONTAÑO DAVID ALEXANDER</t>
   </si>
   <si>
-    <t>TOVAR AREVALO JULIAN GIOVANNI</t>
-  </si>
-  <si>
     <t>DIONISIO NAVARRETE JOHAN ANDREY</t>
   </si>
   <si>
@@ -135,67 +143,46 @@
     <t>MICHEL STEVEN HERNANDEZ ROJAS</t>
   </si>
   <si>
-    <t>360,000 VALES</t>
-  </si>
-  <si>
-    <t>250,000 PRESTAMO+7,000 CARITAS</t>
-  </si>
-  <si>
-    <t>40,798 UTILIDADES+63,000 CARITAS+700,000 BONO+30,000 DOTACION+20,000 SUGERIDOS</t>
-  </si>
-  <si>
-    <t>1 DIA VC+56,000 CARITAS+300,000 BONO+20,000 SUGERIDOS</t>
-  </si>
-  <si>
-    <t>19,000 SUGERIDOS+102,320 INVENTARIO</t>
-  </si>
-  <si>
-    <t>196,694 COMISION</t>
-  </si>
-  <si>
-    <t>14,000 CARITAS</t>
-  </si>
-  <si>
-    <t>VAC</t>
-  </si>
-  <si>
-    <t>113,000 VALES+1 DIA AUSEN+1 DOMINICAL+49,000 CARITAS+20,822 VALES</t>
-  </si>
-  <si>
-    <t>210,200 PRESTAMO+42,000 CARITAS</t>
-  </si>
-  <si>
-    <t>180,833 PRESTAMO+7,000 CARITAS+3000 SUGERIDOS</t>
-  </si>
-  <si>
-    <t>RENUNCIA 20 AGOS+60,000 VALES+50,000 CAMISA DOTACION ROTA+2,500 UTILIDADES+14,000 CARITAS+14,000 SUGERIDOS</t>
-  </si>
-  <si>
-    <t>100,363 CARITAS+50,000 DOTACION</t>
-  </si>
-  <si>
-    <t>140,000 VALES+21,000 CARITAS+10,000 DOTACION+48,586 VALES</t>
-  </si>
-  <si>
-    <t>INGRESO EL 27 AGOS</t>
-  </si>
-  <si>
-    <t>213,600 PRESTAMO+28,000 CARITAS+10,000 DOTACION+4,000 SUGERIDOS+237,974 VALES</t>
-  </si>
-  <si>
-    <t>89,297 UTILIDADES+42,000 CARITAS+10,000 DOTACION+12,000 SUGERIDOS+228,860 VALES</t>
-  </si>
-  <si>
-    <t>56,000 CARITAS+10,000 DOTACION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8,808 UTILIDADES+56,000 DANIEL+10,000 DOTACION+32,000 SUGERIDOS+547.274 VALES </t>
-  </si>
-  <si>
-    <t>DEVOL VACACIONES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109,376 ABONA A VALES </t>
+    <t>1,000,000 VALES</t>
+  </si>
+  <si>
+    <t>35,300 COOSERPARK+280,600 PRESTAMO+186,329 VALES + 36,100 VALE PENDIENTE</t>
+  </si>
+  <si>
+    <t>44,700 COOSERPARK+224,299 VALES +59,055 VALE PENDIENTE</t>
+  </si>
+  <si>
+    <t>1 DIA LCNR</t>
+  </si>
+  <si>
+    <t>44,700 COOSERPARK + VACACIONES + 2 DIAS INCAPACIDAD</t>
+  </si>
+  <si>
+    <t>35,300 COOSERPARK +389,890 VALES</t>
+  </si>
+  <si>
+    <t>REN 05/SEP</t>
+  </si>
+  <si>
+    <t>207,550 VALES</t>
+  </si>
+  <si>
+    <t>VAC 5 DIAS (INFORMATIVO PAGAR 408,183 VACACIONES)</t>
+  </si>
+  <si>
+    <t>90,000 VALES</t>
+  </si>
+  <si>
+    <t>206,800 PRESTAMO</t>
+  </si>
+  <si>
+    <t>1 DIA LCNR +177,999 PRESTAMO + 1,032 VALES</t>
+  </si>
+  <si>
+    <t>1 DIA LCNR + 200,000 VALES</t>
+  </si>
+  <si>
+    <t>280,000 VALES</t>
   </si>
 </sst>
 </file>
@@ -256,17 +243,15 @@
     </font>
     <font>
       <b/>
-      <u val="singleAccounting"/>
-      <sz val="9"/>
+      <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Century Gothic"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="Aptos Narrow"/>
+      <name val="Century Gothic"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -283,7 +268,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -319,6 +304,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -327,7 +323,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -386,35 +382,23 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="166" fontId="6" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="2" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="166" fontId="8" fillId="2" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -754,7 +738,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E263F044-EB2C-4A38-BF1B-A61CE6B829F6}">
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.140625" style="16" customWidth="1"/>
@@ -807,7 +791,7 @@
         <v>9</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L1" s="8" t="s">
         <v>10</v>
@@ -816,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="N1" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O1" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P1" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A2" s="11">
         <v>52114146</v>
       </c>
@@ -842,18 +826,18 @@
         <v>0</v>
       </c>
       <c r="F2" s="13">
-        <v>640000.00000000012</v>
+        <v>0</v>
       </c>
       <c r="G2" s="13">
         <v>0</v>
       </c>
-      <c r="H2" s="13">
-        <v>360000</v>
-      </c>
-      <c r="I2" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="J2" s="13">
+      <c r="H2" s="21">
+        <v>1000000</v>
+      </c>
+      <c r="I2" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="J2" s="24">
         <v>3000000.0000000005</v>
       </c>
       <c r="K2" s="13">
@@ -865,16 +849,16 @@
       <c r="M2" s="13">
         <v>0</v>
       </c>
-      <c r="N2" s="14">
-        <v>0</v>
-      </c>
-      <c r="O2" s="22"/>
+      <c r="N2" s="13">
+        <v>0</v>
+      </c>
+      <c r="O2" s="20"/>
       <c r="P2" s="14">
         <f>L2-M2-N2</f>
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="27" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
         <v>94288721</v>
       </c>
@@ -891,37 +875,40 @@
         <v>0</v>
       </c>
       <c r="F3" s="13">
-        <v>140072.4</v>
+        <v>0</v>
       </c>
       <c r="G3" s="13">
-        <v>700000</v>
-      </c>
-      <c r="H3" s="13"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="13">
-        <v>1559927.6</v>
+        <v>0</v>
+      </c>
+      <c r="H3" s="21">
+        <f>280600+186329+36100</f>
+        <v>503029</v>
+      </c>
+      <c r="I3" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="J3" s="25">
+        <v>461671</v>
       </c>
       <c r="K3" s="13">
-        <v>1550000</v>
+        <v>0</v>
       </c>
       <c r="L3" s="13">
-        <v>850000</v>
+        <v>0</v>
       </c>
       <c r="M3" s="13">
-        <v>28000</v>
-      </c>
-      <c r="N3" s="14">
-        <v>465574</v>
-      </c>
-      <c r="O3" s="22" t="s">
-        <v>51</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N3" s="13">
+        <v>0</v>
+      </c>
+      <c r="O3" s="20"/>
       <c r="P3" s="14">
         <f>L3-M3-N3</f>
-        <v>356426</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" ht="27" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
         <v>1001200622</v>
       </c>
@@ -938,37 +925,40 @@
         <v>0</v>
       </c>
       <c r="F4" s="13">
-        <v>140072.4</v>
+        <v>0</v>
       </c>
       <c r="G4" s="13">
-        <v>600000</v>
-      </c>
-      <c r="H4" s="13"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="13">
-        <v>1459927.6</v>
+        <v>0</v>
+      </c>
+      <c r="H4" s="21">
+        <f>200000+24299+59055</f>
+        <v>283354</v>
+      </c>
+      <c r="I4" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="J4" s="25">
+        <v>671946</v>
       </c>
       <c r="K4" s="13">
-        <v>1250000</v>
+        <v>0</v>
       </c>
       <c r="L4" s="13">
-        <v>650000</v>
+        <v>0</v>
       </c>
       <c r="M4" s="13">
-        <v>42000</v>
-      </c>
-      <c r="N4" s="14">
-        <v>340157</v>
-      </c>
-      <c r="O4" s="25" t="s">
-        <v>52</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N4" s="13">
+        <v>0</v>
+      </c>
+      <c r="O4" s="20"/>
       <c r="P4" s="14">
-        <f t="shared" ref="P4:P19" si="0">L4-M4-N4</f>
-        <v>267843</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+        <f t="shared" ref="P4:P18" si="0">L4-M4-N4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
         <v>1001045472</v>
       </c>
@@ -985,37 +975,37 @@
         <v>0</v>
       </c>
       <c r="F5" s="13">
-        <v>135403.32</v>
+        <v>0</v>
       </c>
       <c r="G5" s="13">
-        <v>700000</v>
-      </c>
-      <c r="H5" s="13"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="13">
-        <v>1564596.68</v>
+        <v>0</v>
+      </c>
+      <c r="H5" s="21">
+        <v>0</v>
+      </c>
+      <c r="I5" s="22"/>
+      <c r="J5" s="25">
+        <v>1000000</v>
       </c>
       <c r="K5" s="13">
-        <v>1269670</v>
+        <v>0</v>
       </c>
       <c r="L5" s="13">
-        <v>569670</v>
+        <v>0</v>
       </c>
       <c r="M5" s="13">
-        <v>56000</v>
-      </c>
-      <c r="N5" s="14">
-        <v>10000</v>
-      </c>
-      <c r="O5" s="22" t="s">
-        <v>53</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N5" s="13">
+        <v>0</v>
+      </c>
+      <c r="O5" s="20"/>
       <c r="P5" s="14">
         <f t="shared" si="0"/>
-        <v>503670</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" ht="27" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
         <v>80875830</v>
       </c>
@@ -1023,46 +1013,48 @@
         <v>17</v>
       </c>
       <c r="C6" s="4">
-        <v>875452.5</v>
+        <v>817089</v>
       </c>
       <c r="D6" s="5">
-        <v>124547.49999999999</v>
+        <v>116244.33333333333</v>
       </c>
       <c r="E6" s="13">
         <v>0</v>
       </c>
       <c r="F6" s="13">
-        <v>126065.16</v>
+        <v>0</v>
       </c>
       <c r="G6" s="13">
-        <v>700000</v>
-      </c>
-      <c r="H6" s="13"/>
-      <c r="I6" s="23"/>
-      <c r="J6" s="13">
-        <v>1573934.84</v>
+        <v>0</v>
+      </c>
+      <c r="H6" s="21">
+        <v>0</v>
+      </c>
+      <c r="I6" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="J6" s="25">
+        <v>933333.33333333337</v>
       </c>
       <c r="K6" s="13">
-        <v>1739070</v>
+        <v>0</v>
       </c>
       <c r="L6" s="13">
-        <v>1039070</v>
+        <v>0</v>
       </c>
       <c r="M6" s="13">
-        <v>56000</v>
-      </c>
-      <c r="N6" s="14">
-        <v>598082</v>
-      </c>
-      <c r="O6" s="22" t="s">
-        <v>54</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N6" s="13">
+        <v>0</v>
+      </c>
+      <c r="O6" s="20"/>
       <c r="P6" s="14">
         <f t="shared" si="0"/>
-        <v>384988</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
         <v>1006116706</v>
       </c>
@@ -1073,25 +1065,25 @@
         <v>875452.5</v>
       </c>
       <c r="D7" s="5">
-        <v>124547.49999999999</v>
+        <v>58122.166666666664</v>
       </c>
       <c r="E7" s="13">
         <v>0</v>
       </c>
       <c r="F7" s="13">
-        <v>140072.4</v>
+        <v>0</v>
       </c>
       <c r="G7" s="13">
-        <v>100000</v>
-      </c>
-      <c r="H7" s="13">
-        <v>257000</v>
-      </c>
-      <c r="I7" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="J7" s="13">
-        <v>702927.6</v>
+        <v>0</v>
+      </c>
+      <c r="H7" s="21">
+        <v>0</v>
+      </c>
+      <c r="I7" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="J7" s="25">
+        <v>888874.66666666663</v>
       </c>
       <c r="K7" s="13">
         <v>0</v>
@@ -1102,16 +1094,16 @@
       <c r="M7" s="13">
         <v>0</v>
       </c>
-      <c r="N7" s="14">
-        <v>0</v>
-      </c>
-      <c r="O7" s="23"/>
+      <c r="N7" s="13">
+        <v>0</v>
+      </c>
+      <c r="O7" s="20"/>
       <c r="P7" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="27" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
         <v>1193092448</v>
       </c>
@@ -1128,19 +1120,19 @@
         <v>0</v>
       </c>
       <c r="F8" s="13">
-        <v>140072.4</v>
+        <v>0</v>
       </c>
       <c r="G8" s="13">
-        <v>700000</v>
-      </c>
-      <c r="H8" s="13">
-        <v>853798</v>
-      </c>
-      <c r="I8" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="J8" s="13">
-        <v>706129.6</v>
+        <v>0</v>
+      </c>
+      <c r="H8" s="21">
+        <v>389890</v>
+      </c>
+      <c r="I8" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="J8" s="25">
+        <v>574810</v>
       </c>
       <c r="K8" s="13">
         <v>0</v>
@@ -1151,16 +1143,16 @@
       <c r="M8" s="13">
         <v>0</v>
       </c>
-      <c r="N8" s="14">
-        <v>0</v>
-      </c>
-      <c r="O8" s="25"/>
+      <c r="N8" s="13">
+        <v>0</v>
+      </c>
+      <c r="O8" s="20"/>
       <c r="P8" s="14">
         <f>L8-M8-N8</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
         <v>79910037</v>
       </c>
@@ -1168,28 +1160,26 @@
         <v>20</v>
       </c>
       <c r="C9" s="4">
-        <v>817089</v>
+        <v>875452.5</v>
       </c>
       <c r="D9" s="5">
-        <v>116244.33333333333</v>
+        <v>124547.49999999999</v>
       </c>
       <c r="E9" s="13">
         <v>0</v>
       </c>
       <c r="F9" s="13">
-        <v>135403.32</v>
+        <v>0</v>
       </c>
       <c r="G9" s="13">
-        <v>300000</v>
-      </c>
-      <c r="H9" s="13">
-        <v>376000</v>
-      </c>
-      <c r="I9" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="J9" s="13">
-        <v>721930.01333333342</v>
+        <v>0</v>
+      </c>
+      <c r="H9" s="21">
+        <v>0</v>
+      </c>
+      <c r="I9" s="22"/>
+      <c r="J9" s="25">
+        <v>1000000</v>
       </c>
       <c r="K9" s="13">
         <v>0</v>
@@ -1200,16 +1190,16 @@
       <c r="M9" s="13">
         <v>0</v>
       </c>
-      <c r="N9" s="14">
-        <v>0</v>
-      </c>
-      <c r="O9" s="22"/>
+      <c r="N9" s="13">
+        <v>0</v>
+      </c>
+      <c r="O9" s="20"/>
       <c r="P9" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
         <v>52767162</v>
       </c>
@@ -1217,28 +1207,28 @@
         <v>21</v>
       </c>
       <c r="C10" s="4">
-        <v>875452.5</v>
+        <v>291817.5</v>
       </c>
       <c r="D10" s="5">
-        <v>124547.49999999999</v>
+        <v>41515.833333333328</v>
       </c>
       <c r="E10" s="13">
         <v>0</v>
       </c>
       <c r="F10" s="13">
-        <v>140072.4</v>
+        <v>0</v>
       </c>
       <c r="G10" s="13">
         <v>0</v>
       </c>
-      <c r="H10" s="13">
-        <v>121340</v>
-      </c>
-      <c r="I10" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="J10" s="13">
-        <v>738587.6</v>
+      <c r="H10" s="21">
+        <v>0</v>
+      </c>
+      <c r="I10" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="J10" s="25">
+        <v>333333.33333333331</v>
       </c>
       <c r="K10" s="13">
         <v>0</v>
@@ -1249,16 +1239,16 @@
       <c r="M10" s="13">
         <v>0</v>
       </c>
-      <c r="N10" s="14">
-        <v>0</v>
-      </c>
-      <c r="O10" s="22"/>
+      <c r="N10" s="13">
+        <v>0</v>
+      </c>
+      <c r="O10" s="20"/>
       <c r="P10" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
         <v>1000795016</v>
       </c>
@@ -1275,17 +1265,17 @@
         <v>0</v>
       </c>
       <c r="F11" s="13">
-        <v>172000</v>
+        <v>0</v>
       </c>
       <c r="G11" s="13">
-        <v>850000</v>
-      </c>
-      <c r="H11" s="13"/>
-      <c r="I11" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="J11" s="13">
-        <v>1877547.5</v>
+        <v>0</v>
+      </c>
+      <c r="H11" s="21">
+        <v>0</v>
+      </c>
+      <c r="I11" s="22"/>
+      <c r="J11" s="25">
+        <v>1199547.5</v>
       </c>
       <c r="K11" s="13">
         <v>0</v>
@@ -1296,16 +1286,16 @@
       <c r="M11" s="13">
         <v>0</v>
       </c>
-      <c r="N11" s="14">
-        <v>0</v>
-      </c>
-      <c r="O11" s="23"/>
+      <c r="N11" s="13">
+        <v>0</v>
+      </c>
+      <c r="O11" s="20"/>
       <c r="P11" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
         <v>79593400</v>
       </c>
@@ -1313,7 +1303,7 @@
         <v>23</v>
       </c>
       <c r="C12" s="4">
-        <v>7150000</v>
+        <v>0</v>
       </c>
       <c r="D12" s="5">
         <v>0</v>
@@ -1322,35 +1312,37 @@
         <v>0</v>
       </c>
       <c r="F12" s="13">
-        <v>572000</v>
+        <v>0</v>
       </c>
       <c r="G12" s="13">
-        <v>2000000</v>
-      </c>
-      <c r="H12" s="13"/>
-      <c r="I12" s="26"/>
-      <c r="J12" s="13">
-        <v>8578000</v>
+        <v>0</v>
+      </c>
+      <c r="H12" s="21">
+        <v>0</v>
+      </c>
+      <c r="I12" s="22"/>
+      <c r="J12" s="25">
+        <v>0</v>
       </c>
       <c r="K12" s="13">
         <v>0</v>
       </c>
-      <c r="L12" s="28">
-        <v>572000</v>
+      <c r="L12" s="13">
+        <v>0</v>
       </c>
       <c r="M12" s="13">
         <v>0</v>
       </c>
-      <c r="N12" s="14">
-        <v>0</v>
-      </c>
-      <c r="O12" s="23"/>
+      <c r="N12" s="13">
+        <v>0</v>
+      </c>
+      <c r="O12" s="20"/>
       <c r="P12" s="14">
         <f t="shared" si="0"/>
-        <v>572000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
         <v>1023029896</v>
       </c>
@@ -1367,39 +1359,39 @@
         <v>0</v>
       </c>
       <c r="F13" s="13">
-        <v>140072.4</v>
+        <v>0</v>
       </c>
       <c r="G13" s="13">
-        <v>100000</v>
-      </c>
-      <c r="H13" s="13">
-        <v>14000</v>
-      </c>
-      <c r="I13" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="H13" s="21">
+        <v>207550</v>
+      </c>
+      <c r="I13" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="J13" s="13">
-        <v>945927.6</v>
+      <c r="J13" s="25">
+        <v>792450</v>
       </c>
       <c r="K13" s="13">
         <v>0</v>
       </c>
-      <c r="L13" s="29">
+      <c r="L13" s="13">
         <v>0</v>
       </c>
       <c r="M13" s="13">
         <v>0</v>
       </c>
-      <c r="N13" s="14">
-        <v>0</v>
-      </c>
-      <c r="O13" s="23"/>
+      <c r="N13" s="13">
+        <v>0</v>
+      </c>
+      <c r="O13" s="20"/>
       <c r="P13" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
         <v>1015473856</v>
       </c>
@@ -1407,49 +1399,48 @@
         <v>25</v>
       </c>
       <c r="C14" s="4">
-        <v>366666.66666666663</v>
+        <v>733333.33333333326</v>
       </c>
       <c r="D14" s="5">
-        <v>41515.833333333328</v>
+        <v>83031.666666666657</v>
       </c>
       <c r="E14" s="13">
         <v>0</v>
       </c>
       <c r="F14" s="13">
-        <v>117333.33333333333</v>
+        <v>0</v>
       </c>
       <c r="G14" s="13">
-        <v>600000</v>
-      </c>
-      <c r="H14" s="13"/>
-      <c r="I14" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="H14" s="21">
+        <v>0</v>
+      </c>
+      <c r="I14" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="J14" s="13">
-        <v>890849.16666666663</v>
+      <c r="J14" s="25">
+        <v>816364.99999999988</v>
       </c>
       <c r="K14" s="13">
         <v>0</v>
       </c>
-      <c r="L14" s="28">
-        <f>733333+207579</f>
-        <v>940912</v>
+      <c r="L14" s="13">
+        <v>0</v>
       </c>
       <c r="M14" s="13">
         <v>0</v>
       </c>
-      <c r="N14" s="14">
-        <v>0</v>
-      </c>
-      <c r="O14" s="23" t="s">
-        <v>55</v>
-      </c>
+      <c r="N14" s="13">
+        <v>0</v>
+      </c>
+      <c r="O14" s="20"/>
       <c r="P14" s="14">
         <f t="shared" si="0"/>
-        <v>940912</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" ht="27" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
         <v>1026306646</v>
       </c>
@@ -1457,48 +1448,48 @@
         <v>26</v>
       </c>
       <c r="C15" s="4">
-        <v>758725.5</v>
+        <v>875452.5</v>
       </c>
       <c r="D15" s="5">
-        <v>107941.16666666666</v>
+        <v>124547.49999999999</v>
       </c>
       <c r="E15" s="13">
         <v>0</v>
       </c>
       <c r="F15" s="13">
-        <v>130734.24</v>
+        <v>0</v>
       </c>
       <c r="G15" s="13">
         <v>0</v>
       </c>
-      <c r="H15" s="13">
-        <v>182822</v>
+      <c r="H15" s="21">
+        <v>90000</v>
       </c>
       <c r="I15" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="J15" s="13">
-        <v>553110.42666666664</v>
+      <c r="J15" s="25">
+        <v>910000</v>
       </c>
       <c r="K15" s="13">
         <v>0</v>
       </c>
-      <c r="L15" s="29">
+      <c r="L15" s="13">
         <v>0</v>
       </c>
       <c r="M15" s="13">
         <v>0</v>
       </c>
-      <c r="N15" s="14">
-        <v>0</v>
-      </c>
-      <c r="O15" s="23"/>
+      <c r="N15" s="13">
+        <v>0</v>
+      </c>
+      <c r="O15" s="20"/>
       <c r="P15" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
         <v>1003533086</v>
       </c>
@@ -1512,42 +1503,42 @@
         <v>124547.49999999999</v>
       </c>
       <c r="E16" s="13">
-        <v>337043</v>
+        <v>0</v>
       </c>
       <c r="F16" s="13">
-        <v>140072.4</v>
+        <v>0</v>
       </c>
       <c r="G16" s="13">
         <v>0</v>
       </c>
-      <c r="H16" s="13">
-        <v>252200</v>
+      <c r="H16" s="21">
+        <v>206800</v>
       </c>
       <c r="I16" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="J16" s="13">
-        <v>944770.6</v>
+      <c r="J16" s="25">
+        <v>793200</v>
       </c>
       <c r="K16" s="13">
         <v>0</v>
       </c>
-      <c r="L16" s="29">
+      <c r="L16" s="13">
         <v>0</v>
       </c>
       <c r="M16" s="13">
         <v>0</v>
       </c>
-      <c r="N16" s="14">
-        <v>0</v>
-      </c>
-      <c r="O16" s="23"/>
+      <c r="N16" s="13">
+        <v>0</v>
+      </c>
+      <c r="O16" s="20"/>
       <c r="P16" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
         <v>1028660836</v>
       </c>
@@ -1555,79 +1546,78 @@
         <v>28</v>
       </c>
       <c r="C17" s="4">
-        <v>875452.5</v>
+        <v>817089</v>
       </c>
       <c r="D17" s="5">
-        <v>124547.49999999999</v>
+        <v>116244.33333333333</v>
       </c>
       <c r="E17" s="13">
-        <v>160699</v>
+        <v>0</v>
       </c>
       <c r="F17" s="13">
-        <v>140072.4</v>
+        <v>0</v>
       </c>
       <c r="G17" s="13">
         <v>0</v>
       </c>
-      <c r="H17" s="13">
-        <v>190833</v>
+      <c r="H17" s="21">
+        <f>177999+1032</f>
+        <v>179031</v>
       </c>
       <c r="I17" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="J17" s="13">
-        <v>829793.6</v>
+      <c r="J17" s="25">
+        <v>754302.33333333337</v>
       </c>
       <c r="K17" s="13">
         <v>0</v>
       </c>
-      <c r="L17" s="28">
-        <v>109376</v>
+      <c r="L17" s="13">
+        <v>0</v>
       </c>
       <c r="M17" s="13">
-        <v>109376</v>
-      </c>
-      <c r="N17" s="14">
-        <v>0</v>
-      </c>
-      <c r="O17" s="23" t="s">
-        <v>56</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N17" s="13">
+        <v>0</v>
+      </c>
+      <c r="O17" s="20"/>
       <c r="P17" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="27" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
-        <v>1123436140</v>
+        <v>1053330769</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>29</v>
       </c>
       <c r="C18" s="4">
-        <v>350181</v>
+        <v>817089</v>
       </c>
       <c r="D18" s="5">
-        <v>49819</v>
+        <v>116244.33333333333</v>
       </c>
       <c r="E18" s="13">
         <v>0</v>
       </c>
       <c r="F18" s="13">
-        <v>98050.680000000008</v>
+        <v>0</v>
       </c>
       <c r="G18" s="13">
         <v>0</v>
       </c>
-      <c r="H18" s="13">
-        <v>140500</v>
-      </c>
-      <c r="I18" s="22" t="s">
+      <c r="H18" s="21">
+        <v>200000</v>
+      </c>
+      <c r="I18" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="J18" s="13">
-        <v>161449.32</v>
+      <c r="J18" s="25">
+        <v>733333.33333333337</v>
       </c>
       <c r="K18" s="13">
         <v>0</v>
@@ -1638,21 +1628,21 @@
       <c r="M18" s="13">
         <v>0</v>
       </c>
-      <c r="N18" s="14">
-        <v>0</v>
-      </c>
-      <c r="O18" s="23"/>
+      <c r="N18" s="13">
+        <v>0</v>
+      </c>
+      <c r="O18" s="20"/>
       <c r="P18" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A19" s="11">
-        <v>1053330769</v>
+        <v>1013673759</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C19" s="4">
         <v>875452.5</v>
@@ -1661,22 +1651,22 @@
         <v>124547.49999999999</v>
       </c>
       <c r="E19" s="13">
-        <v>270810</v>
+        <v>0</v>
       </c>
       <c r="F19" s="13">
-        <v>130734.24</v>
+        <v>0</v>
       </c>
       <c r="G19" s="13">
         <v>0</v>
       </c>
-      <c r="H19" s="13">
-        <v>150363</v>
-      </c>
-      <c r="I19" s="22" t="s">
+      <c r="H19" s="21">
+        <v>280000</v>
+      </c>
+      <c r="I19" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="J19" s="13">
-        <v>989712.76</v>
+      <c r="J19" s="25">
+        <v>720000</v>
       </c>
       <c r="K19" s="13">
         <v>0</v>
@@ -1687,18 +1677,17 @@
       <c r="M19" s="13">
         <v>0</v>
       </c>
-      <c r="N19" s="14">
-        <v>0</v>
-      </c>
-      <c r="O19" s="23"/>
+      <c r="N19" s="13">
+        <v>0</v>
+      </c>
+      <c r="O19" s="20"/>
       <c r="P19" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
-        <v>1013673759</v>
+        <v>1003483344</v>
       </c>
       <c r="B20" s="12" t="s">
         <v>34</v>
@@ -1713,19 +1702,17 @@
         <v>0</v>
       </c>
       <c r="F20" s="13">
-        <v>135403.32</v>
+        <v>0</v>
       </c>
       <c r="G20" s="13">
         <v>0</v>
       </c>
-      <c r="H20" s="13">
-        <v>219586</v>
-      </c>
-      <c r="I20" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="J20" s="13">
-        <v>645010.67999999993</v>
+      <c r="H20" s="21">
+        <v>0</v>
+      </c>
+      <c r="I20" s="23"/>
+      <c r="J20" s="25">
+        <v>1000000</v>
       </c>
       <c r="K20" s="13">
         <v>0</v>
@@ -1736,79 +1723,31 @@
       <c r="M20" s="13">
         <v>0</v>
       </c>
-      <c r="N20" s="14">
-        <v>0</v>
-      </c>
-      <c r="O20" s="23"/>
+      <c r="N20" s="13">
+        <v>0</v>
+      </c>
+      <c r="O20" s="20"/>
       <c r="P20" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" s="11">
-        <v>1003483344</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C21" s="4">
-        <v>291817.5</v>
-      </c>
-      <c r="D21" s="5">
-        <v>41515.833333333328</v>
-      </c>
-      <c r="E21" s="13">
-        <v>56313</v>
-      </c>
-      <c r="F21" s="13">
-        <v>23345.4</v>
-      </c>
-      <c r="G21" s="13">
-        <v>0</v>
-      </c>
-      <c r="H21" s="13">
-        <v>0</v>
-      </c>
-      <c r="I21" s="27" t="s">
-        <v>50</v>
-      </c>
-      <c r="J21" s="13">
-        <v>366300.93333333329</v>
-      </c>
-      <c r="K21" s="13">
-        <v>0</v>
-      </c>
-      <c r="L21" s="13">
-        <v>0</v>
-      </c>
-      <c r="M21" s="13">
-        <v>0</v>
-      </c>
-      <c r="N21" s="14">
-        <v>0</v>
-      </c>
-      <c r="O21" s="23"/>
-      <c r="P21" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" s="11"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="13"/>
-      <c r="K22" s="13"/>
-      <c r="L22" s="13"/>
-      <c r="M22" s="13"/>
-      <c r="N22" s="15"/>
-      <c r="O22" s="15"/>
-      <c r="P22" s="15"/>
+      <c r="A21" s="11"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="13"/>
+      <c r="K21" s="13"/>
+      <c r="L21" s="13"/>
+      <c r="M21" s="13"/>
+      <c r="N21" s="15"/>
+      <c r="O21" s="15"/>
+      <c r="P21" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/empleados.xlsx
+++ b/empleados.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\NOMINA Y RRHH\NOMINA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Dropbox\NOMINA Y RRHH\NOMINA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FDC354F-F64C-4EC8-B8A6-4CF89E0B3A45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09547F64-49FA-43F4-8E07-DC68D1B0E382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DA975529-9E83-4FFA-BD35-5CA808A15280}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{DA975529-9E83-4FFA-BD35-5CA808A15280}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -20,23 +20,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t>CEDULA</t>
   </si>
@@ -143,46 +132,73 @@
     <t>MICHEL STEVEN HERNANDEZ ROJAS</t>
   </si>
   <si>
-    <t>1,000,000 VALES</t>
-  </si>
-  <si>
-    <t>35,300 COOSERPARK+280,600 PRESTAMO+186,329 VALES + 36,100 VALE PENDIENTE</t>
-  </si>
-  <si>
-    <t>44,700 COOSERPARK+224,299 VALES +59,055 VALE PENDIENTE</t>
-  </si>
-  <si>
-    <t>1 DIA LCNR</t>
-  </si>
-  <si>
-    <t>44,700 COOSERPARK + VACACIONES + 2 DIAS INCAPACIDAD</t>
-  </si>
-  <si>
-    <t>35,300 COOSERPARK +389,890 VALES</t>
-  </si>
-  <si>
-    <t>REN 05/SEP</t>
-  </si>
-  <si>
-    <t>207,550 VALES</t>
-  </si>
-  <si>
-    <t>VAC 5 DIAS (INFORMATIVO PAGAR 408,183 VACACIONES)</t>
-  </si>
-  <si>
-    <t>90,000 VALES</t>
-  </si>
-  <si>
-    <t>206,800 PRESTAMO</t>
-  </si>
-  <si>
-    <t>1 DIA LCNR +177,999 PRESTAMO + 1,032 VALES</t>
-  </si>
-  <si>
-    <t>1 DIA LCNR + 200,000 VALES</t>
-  </si>
-  <si>
-    <t>280,000 VALES</t>
+    <t>OSWALDO DUCUARA  VERA</t>
+  </si>
+  <si>
+    <t>360,000 vales</t>
+  </si>
+  <si>
+    <t>29,871 exedente vales</t>
+  </si>
+  <si>
+    <t>9 Dias incap</t>
+  </si>
+  <si>
+    <t>Vacaciones+250,000 Prestamo</t>
+  </si>
+  <si>
+    <t>35,000 (5) Caritas+18,000 sugeridos+300,000 Bono</t>
+  </si>
+  <si>
+    <t>7,000 (1) Carita</t>
+  </si>
+  <si>
+    <t>3 Dias incap</t>
+  </si>
+  <si>
+    <t>3 dias incap + renuncia 26 de Agos+56,000 (8) Caritas</t>
+  </si>
+  <si>
+    <t>203,400 Prestamo+42,000 (6) Caritas</t>
+  </si>
+  <si>
+    <t>175,166 Prestamo+28,000 (4) caritas+30,000 sugeridos</t>
+  </si>
+  <si>
+    <t>1 Dia Incp+49,000 (7) Caritas+10,000 1 dia dotacion</t>
+  </si>
+  <si>
+    <t>56,000 (8) Caritas</t>
+  </si>
+  <si>
+    <t>Ing 17 Sep+7,000 (1) carita</t>
+  </si>
+  <si>
+    <t>276,350 Prestamo+56,000 (8) Caritas+10,000 sugeridos+292,161 VALES</t>
+  </si>
+  <si>
+    <t>56,000 (8) CARITAS+14,000 sugeridos+77,000 CAJA + 475,654 VALES</t>
+  </si>
+  <si>
+    <t>200,000 vales+70,000 (10) Caritas + 116,726 2 dias+30,000 3 dias dotacion+12,000 sugeridos</t>
+  </si>
+  <si>
+    <t>35,000 (5) caritas+10,000 1 dia dotacion+20,000 sugeridos+4,441 Utilidades+578,460 VALES</t>
+  </si>
+  <si>
+    <t>28,000 (4) Caritas+ 116,726 2 DIAS+18,000 Sugeridos+16,807 Utilidades+301,524 VALES</t>
+  </si>
+  <si>
+    <t>Se pagan los 3 dias de aux transporte</t>
+  </si>
+  <si>
+    <t>335,324 VALES</t>
+  </si>
+  <si>
+    <t>100,000 VALES+35,000 (5) Caritas</t>
+  </si>
+  <si>
+    <t>PAGO 16 DE SEPTIEMBRE POR NO AFILIACION</t>
   </si>
 </sst>
 </file>
@@ -323,7 +339,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -399,6 +415,12 @@
     </xf>
     <xf numFmtId="166" fontId="8" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -738,7 +760,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E263F044-EB2C-4A38-BF1B-A61CE6B829F6}">
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.140625" style="16" customWidth="1"/>
@@ -826,16 +848,16 @@
         <v>0</v>
       </c>
       <c r="F2" s="13">
-        <v>0</v>
+        <v>640000.00000000012</v>
       </c>
       <c r="G2" s="13">
         <v>0</v>
       </c>
       <c r="H2" s="21">
-        <v>1000000</v>
+        <v>360000</v>
       </c>
       <c r="I2" s="22" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J2" s="24">
         <v>3000000.0000000005</v>
@@ -858,7 +880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" ht="27" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
         <v>94288721</v>
       </c>
@@ -875,40 +897,41 @@
         <v>0</v>
       </c>
       <c r="F3" s="13">
-        <v>0</v>
+        <v>140072.4</v>
       </c>
       <c r="G3" s="13">
-        <v>0</v>
+        <v>700000</v>
       </c>
       <c r="H3" s="21">
-        <f>280600+186329+36100</f>
-        <v>503029</v>
+        <v>29871</v>
       </c>
       <c r="I3" s="22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J3" s="25">
-        <v>461671</v>
+        <v>1530056.6</v>
       </c>
       <c r="K3" s="13">
-        <v>0</v>
+        <v>1334511</v>
       </c>
       <c r="L3" s="13">
-        <v>0</v>
+        <v>634511</v>
       </c>
       <c r="M3" s="13">
-        <v>0</v>
+        <v>56000</v>
       </c>
       <c r="N3" s="13">
-        <v>0</v>
-      </c>
-      <c r="O3" s="20"/>
+        <v>578511</v>
+      </c>
+      <c r="O3" s="20" t="s">
+        <v>49</v>
+      </c>
       <c r="P3" s="14">
-        <f>L3-M3-N3</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
+        <f t="shared" ref="P3:P21" si="0">L3-M3-N3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="27" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
         <v>1001200622</v>
       </c>
@@ -925,40 +948,37 @@
         <v>0</v>
       </c>
       <c r="F4" s="13">
-        <v>0</v>
+        <v>140072.4</v>
       </c>
       <c r="G4" s="13">
-        <v>0</v>
-      </c>
-      <c r="H4" s="21">
-        <f>200000+24299+59055</f>
-        <v>283354</v>
-      </c>
-      <c r="I4" s="22" t="s">
-        <v>37</v>
-      </c>
+        <v>600000</v>
+      </c>
+      <c r="H4" s="21"/>
+      <c r="I4" s="22"/>
       <c r="J4" s="25">
-        <v>671946</v>
+        <v>1459927.6</v>
       </c>
       <c r="K4" s="13">
-        <v>0</v>
+        <v>1250000</v>
       </c>
       <c r="L4" s="13">
-        <v>0</v>
+        <v>650000</v>
       </c>
       <c r="M4" s="13">
-        <v>0</v>
+        <v>56000</v>
       </c>
       <c r="N4" s="13">
-        <v>0</v>
-      </c>
-      <c r="O4" s="20"/>
+        <v>594000</v>
+      </c>
+      <c r="O4" s="26" t="s">
+        <v>50</v>
+      </c>
       <c r="P4" s="14">
-        <f t="shared" ref="P4:P18" si="0">L4-M4-N4</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="27" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
         <v>1001045472</v>
       </c>
@@ -975,37 +995,37 @@
         <v>0</v>
       </c>
       <c r="F5" s="13">
-        <v>0</v>
+        <v>140072.4</v>
       </c>
       <c r="G5" s="13">
-        <v>0</v>
-      </c>
-      <c r="H5" s="21">
-        <v>0</v>
-      </c>
+        <v>700000</v>
+      </c>
+      <c r="H5" s="21"/>
       <c r="I5" s="22"/>
       <c r="J5" s="25">
-        <v>1000000</v>
+        <v>1559927.6</v>
       </c>
       <c r="K5" s="13">
-        <v>0</v>
+        <v>1477558</v>
       </c>
       <c r="L5" s="13">
-        <v>0</v>
+        <v>777558</v>
       </c>
       <c r="M5" s="13">
-        <v>0</v>
+        <v>186726</v>
       </c>
       <c r="N5" s="13">
-        <v>0</v>
-      </c>
-      <c r="O5" s="20"/>
+        <v>242000</v>
+      </c>
+      <c r="O5" s="20" t="s">
+        <v>51</v>
+      </c>
       <c r="P5" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
+        <v>348832</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="27" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
         <v>80875830</v>
       </c>
@@ -1013,45 +1033,45 @@
         <v>17</v>
       </c>
       <c r="C6" s="4">
-        <v>817089</v>
+        <v>875452.5</v>
       </c>
       <c r="D6" s="5">
-        <v>116244.33333333333</v>
+        <v>49819</v>
       </c>
       <c r="E6" s="13">
         <v>0</v>
       </c>
       <c r="F6" s="13">
-        <v>0</v>
+        <v>135403.32</v>
       </c>
       <c r="G6" s="13">
-        <v>0</v>
-      </c>
-      <c r="H6" s="21">
-        <v>0</v>
-      </c>
+        <v>700000</v>
+      </c>
+      <c r="H6" s="21"/>
       <c r="I6" s="22" t="s">
         <v>38</v>
       </c>
       <c r="J6" s="25">
-        <v>933333.33333333337</v>
+        <v>1489868.18</v>
       </c>
       <c r="K6" s="13">
-        <v>0</v>
+        <v>2289070</v>
       </c>
       <c r="L6" s="13">
-        <v>0</v>
+        <v>1589070</v>
       </c>
       <c r="M6" s="13">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="N6" s="13">
-        <v>0</v>
-      </c>
-      <c r="O6" s="20"/>
+        <v>612901</v>
+      </c>
+      <c r="O6" s="20" t="s">
+        <v>52</v>
+      </c>
       <c r="P6" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>941169</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
@@ -1071,19 +1091,19 @@
         <v>0</v>
       </c>
       <c r="F7" s="13">
-        <v>0</v>
+        <v>140072.4</v>
       </c>
       <c r="G7" s="13">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="H7" s="21">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="I7" s="22" t="s">
         <v>39</v>
       </c>
       <c r="J7" s="25">
-        <v>888874.66666666663</v>
+        <v>643502.2666666666</v>
       </c>
       <c r="K7" s="13">
         <v>0</v>
@@ -1097,13 +1117,13 @@
       <c r="N7" s="13">
         <v>0</v>
       </c>
-      <c r="O7" s="20"/>
+      <c r="O7" s="27"/>
       <c r="P7" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" ht="27" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
         <v>1193092448</v>
       </c>
@@ -1120,36 +1140,34 @@
         <v>0</v>
       </c>
       <c r="F8" s="13">
-        <v>0</v>
+        <v>140072.4</v>
       </c>
       <c r="G8" s="13">
-        <v>0</v>
-      </c>
-      <c r="H8" s="21">
-        <v>389890</v>
-      </c>
-      <c r="I8" s="22" t="s">
-        <v>40</v>
-      </c>
+        <v>700000</v>
+      </c>
+      <c r="H8" s="21"/>
+      <c r="I8" s="22"/>
       <c r="J8" s="25">
-        <v>574810</v>
+        <v>1559927.6</v>
       </c>
       <c r="K8" s="13">
-        <v>0</v>
+        <v>1250000</v>
       </c>
       <c r="L8" s="13">
-        <v>0</v>
+        <v>550000</v>
       </c>
       <c r="M8" s="13">
-        <v>0</v>
+        <v>144726</v>
       </c>
       <c r="N8" s="13">
-        <v>0</v>
-      </c>
-      <c r="O8" s="20"/>
+        <v>336331</v>
+      </c>
+      <c r="O8" s="26" t="s">
+        <v>53</v>
+      </c>
       <c r="P8" s="14">
-        <f>L8-M8-N8</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>68943</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
@@ -1169,23 +1187,25 @@
         <v>0</v>
       </c>
       <c r="F9" s="13">
-        <v>0</v>
+        <v>140072.4</v>
       </c>
       <c r="G9" s="13">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="H9" s="21">
-        <v>0</v>
-      </c>
-      <c r="I9" s="22"/>
+        <v>353000</v>
+      </c>
+      <c r="I9" s="22" t="s">
+        <v>40</v>
+      </c>
       <c r="J9" s="25">
-        <v>1000000</v>
+        <v>806927.6</v>
       </c>
       <c r="K9" s="13">
         <v>0</v>
       </c>
       <c r="L9" s="13">
-        <v>0</v>
+        <v>-300000</v>
       </c>
       <c r="M9" s="13">
         <v>0</v>
@@ -1196,7 +1216,7 @@
       <c r="O9" s="20"/>
       <c r="P9" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-300000</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
@@ -1207,10 +1227,10 @@
         <v>21</v>
       </c>
       <c r="C10" s="4">
-        <v>291817.5</v>
+        <v>0</v>
       </c>
       <c r="D10" s="5">
-        <v>41515.833333333328</v>
+        <v>0</v>
       </c>
       <c r="E10" s="13">
         <v>0</v>
@@ -1221,14 +1241,10 @@
       <c r="G10" s="13">
         <v>0</v>
       </c>
-      <c r="H10" s="21">
-        <v>0</v>
-      </c>
-      <c r="I10" s="22" t="s">
-        <v>41</v>
-      </c>
+      <c r="H10" s="21"/>
+      <c r="I10" s="22"/>
       <c r="J10" s="25">
-        <v>333333.33333333331</v>
+        <v>0</v>
       </c>
       <c r="K10" s="13">
         <v>0</v>
@@ -1265,23 +1281,21 @@
         <v>0</v>
       </c>
       <c r="F11" s="13">
-        <v>0</v>
+        <v>172000</v>
       </c>
       <c r="G11" s="13">
-        <v>0</v>
-      </c>
-      <c r="H11" s="21">
-        <v>0</v>
-      </c>
+        <v>850000</v>
+      </c>
+      <c r="H11" s="21"/>
       <c r="I11" s="22"/>
       <c r="J11" s="25">
-        <v>1199547.5</v>
+        <v>1877547.5</v>
       </c>
       <c r="K11" s="13">
         <v>0</v>
       </c>
       <c r="L11" s="13">
-        <v>0</v>
+        <v>226987</v>
       </c>
       <c r="M11" s="13">
         <v>0</v>
@@ -1289,10 +1303,10 @@
       <c r="N11" s="13">
         <v>0</v>
       </c>
-      <c r="O11" s="20"/>
+      <c r="O11" s="27"/>
       <c r="P11" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>226987</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
@@ -1303,7 +1317,7 @@
         <v>23</v>
       </c>
       <c r="C12" s="4">
-        <v>0</v>
+        <v>7150000</v>
       </c>
       <c r="D12" s="5">
         <v>0</v>
@@ -1312,23 +1326,21 @@
         <v>0</v>
       </c>
       <c r="F12" s="13">
-        <v>0</v>
+        <v>572000</v>
       </c>
       <c r="G12" s="13">
-        <v>0</v>
-      </c>
-      <c r="H12" s="21">
-        <v>0</v>
-      </c>
+        <v>2000000</v>
+      </c>
+      <c r="H12" s="21"/>
       <c r="I12" s="22"/>
       <c r="J12" s="25">
-        <v>0</v>
+        <v>8578000</v>
       </c>
       <c r="K12" s="13">
         <v>0</v>
       </c>
       <c r="L12" s="13">
-        <v>0</v>
+        <v>572000</v>
       </c>
       <c r="M12" s="13">
         <v>0</v>
@@ -1336,10 +1348,10 @@
       <c r="N12" s="13">
         <v>0</v>
       </c>
-      <c r="O12" s="20"/>
+      <c r="O12" s="27"/>
       <c r="P12" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>572000</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
@@ -1359,19 +1371,19 @@
         <v>0</v>
       </c>
       <c r="F13" s="13">
-        <v>0</v>
+        <v>140072.4</v>
       </c>
       <c r="G13" s="13">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="H13" s="21">
-        <v>207550</v>
+        <v>7000</v>
       </c>
       <c r="I13" s="22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J13" s="25">
-        <v>792450</v>
+        <v>952927.6</v>
       </c>
       <c r="K13" s="13">
         <v>0</v>
@@ -1385,7 +1397,7 @@
       <c r="N13" s="13">
         <v>0</v>
       </c>
-      <c r="O13" s="20"/>
+      <c r="O13" s="27"/>
       <c r="P13" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1399,34 +1411,32 @@
         <v>25</v>
       </c>
       <c r="C14" s="4">
-        <v>733333.33333333326</v>
+        <v>1100000</v>
       </c>
       <c r="D14" s="5">
-        <v>83031.666666666657</v>
+        <v>99638</v>
       </c>
       <c r="E14" s="13">
         <v>0</v>
       </c>
       <c r="F14" s="13">
-        <v>0</v>
+        <v>146666.66666666666</v>
       </c>
       <c r="G14" s="13">
-        <v>0</v>
-      </c>
-      <c r="H14" s="21">
-        <v>0</v>
-      </c>
+        <v>600000</v>
+      </c>
+      <c r="H14" s="21"/>
       <c r="I14" s="22" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J14" s="25">
-        <v>816364.99999999988</v>
+        <v>1652971.3333333333</v>
       </c>
       <c r="K14" s="13">
         <v>0</v>
       </c>
       <c r="L14" s="13">
-        <v>0</v>
+        <v>24910</v>
       </c>
       <c r="M14" s="13">
         <v>0</v>
@@ -1434,10 +1444,12 @@
       <c r="N14" s="13">
         <v>0</v>
       </c>
-      <c r="O14" s="20"/>
+      <c r="O14" s="27" t="s">
+        <v>54</v>
+      </c>
       <c r="P14" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24910</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
@@ -1448,28 +1460,28 @@
         <v>26</v>
       </c>
       <c r="C15" s="4">
-        <v>875452.5</v>
+        <v>641998.5</v>
       </c>
       <c r="D15" s="5">
-        <v>124547.49999999999</v>
+        <v>66425.333333333328</v>
       </c>
       <c r="E15" s="13">
-        <v>0</v>
+        <v>80612</v>
       </c>
       <c r="F15" s="13">
-        <v>0</v>
+        <v>121396.08</v>
       </c>
       <c r="G15" s="13">
         <v>0</v>
       </c>
       <c r="H15" s="21">
-        <v>90000</v>
+        <v>56000</v>
       </c>
       <c r="I15" s="22" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J15" s="25">
-        <v>910000</v>
+        <v>611639.75333333341</v>
       </c>
       <c r="K15" s="13">
         <v>0</v>
@@ -1483,7 +1495,7 @@
       <c r="N15" s="13">
         <v>0</v>
       </c>
-      <c r="O15" s="20"/>
+      <c r="O15" s="27"/>
       <c r="P15" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1503,22 +1515,22 @@
         <v>124547.49999999999</v>
       </c>
       <c r="E16" s="13">
-        <v>0</v>
+        <v>316367</v>
       </c>
       <c r="F16" s="13">
-        <v>0</v>
+        <v>140072.4</v>
       </c>
       <c r="G16" s="13">
         <v>0</v>
       </c>
       <c r="H16" s="21">
-        <v>206800</v>
+        <v>245400</v>
       </c>
       <c r="I16" s="22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J16" s="25">
-        <v>793200</v>
+        <v>930894.6</v>
       </c>
       <c r="K16" s="13">
         <v>0</v>
@@ -1532,7 +1544,7 @@
       <c r="N16" s="13">
         <v>0</v>
       </c>
-      <c r="O16" s="20"/>
+      <c r="O16" s="27"/>
       <c r="P16" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1546,43 +1558,44 @@
         <v>28</v>
       </c>
       <c r="C17" s="4">
-        <v>817089</v>
+        <v>875452.5</v>
       </c>
       <c r="D17" s="5">
-        <v>116244.33333333333</v>
+        <v>124547.49999999999</v>
       </c>
       <c r="E17" s="13">
-        <v>0</v>
+        <v>60861</v>
       </c>
       <c r="F17" s="13">
-        <v>0</v>
+        <v>135403.32</v>
       </c>
       <c r="G17" s="13">
         <v>0</v>
       </c>
       <c r="H17" s="21">
-        <f>177999+1032</f>
-        <v>179031</v>
+        <v>233166</v>
       </c>
       <c r="I17" s="22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J17" s="25">
-        <v>754302.33333333337</v>
+        <v>692291.67999999993</v>
       </c>
       <c r="K17" s="13">
         <v>0</v>
       </c>
       <c r="L17" s="13">
-        <v>0</v>
+        <v>335324</v>
       </c>
       <c r="M17" s="13">
         <v>0</v>
       </c>
       <c r="N17" s="13">
-        <v>0</v>
-      </c>
-      <c r="O17" s="20"/>
+        <v>335324</v>
+      </c>
+      <c r="O17" s="27" t="s">
+        <v>55</v>
+      </c>
       <c r="P17" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1596,28 +1609,28 @@
         <v>29</v>
       </c>
       <c r="C18" s="4">
-        <v>817089</v>
+        <v>875452.5</v>
       </c>
       <c r="D18" s="5">
         <v>116244.33333333333</v>
       </c>
       <c r="E18" s="13">
-        <v>0</v>
+        <v>280770</v>
       </c>
       <c r="F18" s="13">
-        <v>0</v>
+        <v>135403.32</v>
       </c>
       <c r="G18" s="13">
         <v>0</v>
       </c>
       <c r="H18" s="21">
-        <v>200000</v>
+        <v>59000</v>
       </c>
       <c r="I18" s="23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J18" s="25">
-        <v>733333.33333333337</v>
+        <v>1078063.5133333334</v>
       </c>
       <c r="K18" s="13">
         <v>0</v>
@@ -1631,7 +1644,7 @@
       <c r="N18" s="13">
         <v>0</v>
       </c>
-      <c r="O18" s="20"/>
+      <c r="O18" s="27"/>
       <c r="P18" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1654,35 +1667,34 @@
         <v>0</v>
       </c>
       <c r="F19" s="13">
-        <v>0</v>
+        <v>140072.4</v>
       </c>
       <c r="G19" s="13">
         <v>0</v>
       </c>
-      <c r="H19" s="21">
-        <v>280000</v>
-      </c>
-      <c r="I19" s="23" t="s">
-        <v>48</v>
-      </c>
+      <c r="H19" s="21"/>
+      <c r="I19" s="23"/>
       <c r="J19" s="25">
-        <v>720000</v>
+        <v>859927.6</v>
       </c>
       <c r="K19" s="13">
         <v>0</v>
       </c>
       <c r="L19" s="13">
-        <v>0</v>
+        <v>519510</v>
       </c>
       <c r="M19" s="13">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="N19" s="13">
-        <v>0</v>
-      </c>
-      <c r="O19" s="20"/>
+        <v>100000</v>
+      </c>
+      <c r="O19" s="27" t="s">
+        <v>56</v>
+      </c>
       <c r="P19" s="14">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>384510</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
@@ -1699,20 +1711,22 @@
         <v>124547.49999999999</v>
       </c>
       <c r="E20" s="13">
-        <v>0</v>
+        <v>314406</v>
       </c>
       <c r="F20" s="13">
-        <v>0</v>
+        <v>140072.4</v>
       </c>
       <c r="G20" s="13">
         <v>0</v>
       </c>
       <c r="H20" s="21">
-        <v>0</v>
-      </c>
-      <c r="I20" s="23"/>
+        <v>56000</v>
+      </c>
+      <c r="I20" s="23" t="s">
+        <v>47</v>
+      </c>
       <c r="J20" s="25">
-        <v>1000000</v>
+        <v>1118333.6000000001</v>
       </c>
       <c r="K20" s="13">
         <v>0</v>
@@ -1726,28 +1740,80 @@
       <c r="N20" s="13">
         <v>0</v>
       </c>
-      <c r="O20" s="20"/>
+      <c r="O20" s="27"/>
       <c r="P20" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" s="11"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="13"/>
-      <c r="L21" s="13"/>
-      <c r="M21" s="13"/>
-      <c r="N21" s="15"/>
-      <c r="O21" s="15"/>
-      <c r="P21" s="15"/>
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="11">
+        <v>1119210446</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" s="4">
+        <v>817089</v>
+      </c>
+      <c r="D21" s="5">
+        <v>116244.33333333333</v>
+      </c>
+      <c r="E21" s="13">
+        <v>171914</v>
+      </c>
+      <c r="F21" s="13">
+        <v>65367.12</v>
+      </c>
+      <c r="G21" s="13">
+        <v>0</v>
+      </c>
+      <c r="H21" s="21">
+        <v>7000</v>
+      </c>
+      <c r="I21" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="J21" s="25">
+        <v>1032880.2133333335</v>
+      </c>
+      <c r="K21" s="13">
+        <v>0</v>
+      </c>
+      <c r="L21" s="13">
+        <v>66666.666666666672</v>
+      </c>
+      <c r="M21" s="13">
+        <v>0</v>
+      </c>
+      <c r="N21" s="13">
+        <v>0</v>
+      </c>
+      <c r="O21" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="P21" s="14">
+        <f t="shared" si="0"/>
+        <v>66666.666666666672</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A22" s="11"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="13"/>
+      <c r="K22" s="13"/>
+      <c r="L22" s="13"/>
+      <c r="M22" s="13"/>
+      <c r="N22" s="15"/>
+      <c r="O22" s="15"/>
+      <c r="P22" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/empleados.xlsx
+++ b/empleados.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Dropbox\NOMINA Y RRHH\NOMINA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\NOMINA Y RRHH\NOMINA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09547F64-49FA-43F4-8E07-DC68D1B0E382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82092603-9660-4E23-AE92-9BBB33E4BCE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{DA975529-9E83-4FFA-BD35-5CA808A15280}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DA975529-9E83-4FFA-BD35-5CA808A15280}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
   <si>
     <t>CEDULA</t>
   </si>
@@ -123,9 +134,6 @@
     <t>DESCUENTOS EF</t>
   </si>
   <si>
-    <t>COMISIONES TOTALES</t>
-  </si>
-  <si>
     <t>BRYAN ALEJANDRO SANCHEZ GARCIA</t>
   </si>
   <si>
@@ -199,6 +207,30 @@
   </si>
   <si>
     <t>PAGO 16 DE SEPTIEMBRE POR NO AFILIACION</t>
+  </si>
+  <si>
+    <t>VENTAS TOTALES</t>
+  </si>
+  <si>
+    <t>RENTABILIDAD</t>
+  </si>
+  <si>
+    <t>CARTERA</t>
+  </si>
+  <si>
+    <t>PORCENTAJE VENTAS</t>
+  </si>
+  <si>
+    <t>PORCENTAJE RENTABILIDAD</t>
+  </si>
+  <si>
+    <t>PORCENTAJE CARTERA</t>
+  </si>
+  <si>
+    <t>PORCENTAJE COMISION</t>
+  </si>
+  <si>
+    <t>COMISION TOTAL</t>
   </si>
 </sst>
 </file>
@@ -332,14 +364,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="5">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -422,13 +455,17 @@
     <xf numFmtId="166" fontId="6" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="5">
+  <cellStyles count="6">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Moneda 2" xfId="2" xr:uid="{0605646B-B80A-4C57-B156-94B9E01436E0}"/>
     <cellStyle name="Moneda 3" xfId="3" xr:uid="{98C3700D-6BEC-4FA1-B713-C553F57461CF}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2 2 2" xfId="4" xr:uid="{313DBE52-1F1C-482D-97AD-A9EF19D1DCEE}"/>
+    <cellStyle name="Porcentaje" xfId="5" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -760,7 +797,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E263F044-EB2C-4A38-BF1B-A61CE6B829F6}">
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.140625" style="16" customWidth="1"/>
@@ -773,15 +810,22 @@
     <col min="8" max="8" width="13.85546875" style="18" customWidth="1"/>
     <col min="9" max="9" width="61.140625" style="19" customWidth="1"/>
     <col min="10" max="10" width="15" style="18" customWidth="1"/>
-    <col min="11" max="12" width="19.85546875" style="18" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.140625" style="18" customWidth="1"/>
-    <col min="14" max="14" width="15.28515625" style="10" customWidth="1"/>
-    <col min="15" max="15" width="44.5703125" style="10" customWidth="1"/>
-    <col min="16" max="16" width="15.85546875" style="10" customWidth="1"/>
-    <col min="17" max="16384" width="11.42578125" style="10"/>
+    <col min="11" max="11" width="19.85546875" style="18" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.140625" style="18" customWidth="1"/>
+    <col min="13" max="13" width="15.28515625" style="10" customWidth="1"/>
+    <col min="14" max="14" width="44.5703125" style="10" customWidth="1"/>
+    <col min="15" max="16" width="15.85546875" style="10" customWidth="1"/>
+    <col min="17" max="17" width="17.7109375" style="10" customWidth="1"/>
+    <col min="18" max="18" width="15.85546875" style="10" customWidth="1"/>
+    <col min="19" max="19" width="22.5703125" style="10" customWidth="1"/>
+    <col min="20" max="20" width="15.85546875" style="10" customWidth="1"/>
+    <col min="21" max="21" width="18.7109375" style="10" customWidth="1"/>
+    <col min="22" max="22" width="15.85546875" style="18" customWidth="1"/>
+    <col min="23" max="23" width="20.140625" style="10" customWidth="1"/>
+    <col min="24" max="16384" width="11.42578125" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -813,25 +857,46 @@
         <v>9</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="8" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="9" t="s">
+        <v>31</v>
+      </c>
       <c r="N1" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O1" s="9" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="P1" s="9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+      <c r="Q1" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="R1" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="S1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="T1" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="U1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="V1" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="W1" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A2" s="11">
         <v>52114146</v>
       </c>
@@ -857,7 +922,7 @@
         <v>360000</v>
       </c>
       <c r="I2" s="22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J2" s="24">
         <v>3000000.0000000005</v>
@@ -871,16 +936,23 @@
       <c r="M2" s="13">
         <v>0</v>
       </c>
-      <c r="N2" s="13">
-        <v>0</v>
-      </c>
-      <c r="O2" s="20"/>
-      <c r="P2" s="14">
-        <f>L2-M2-N2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" ht="27" x14ac:dyDescent="0.25">
+      <c r="N2" s="20"/>
+      <c r="O2" s="14">
+        <f>K2-L2-M2</f>
+        <v>0</v>
+      </c>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="28"/>
+      <c r="R2" s="28"/>
+      <c r="S2" s="28"/>
+      <c r="T2" s="14"/>
+      <c r="U2" s="28"/>
+      <c r="V2" s="13">
+        <v>0</v>
+      </c>
+      <c r="W2" s="28"/>
+    </row>
+    <row r="3" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
         <v>94288721</v>
       </c>
@@ -906,32 +978,39 @@
         <v>29871</v>
       </c>
       <c r="I3" s="22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J3" s="25">
         <v>1530056.6</v>
       </c>
       <c r="K3" s="13">
+        <v>634511</v>
+      </c>
+      <c r="L3" s="13">
+        <v>56000</v>
+      </c>
+      <c r="M3" s="13">
+        <v>578511</v>
+      </c>
+      <c r="N3" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="O3" s="14">
+        <f t="shared" ref="O3:O21" si="0">K3-L3-M3</f>
+        <v>0</v>
+      </c>
+      <c r="P3" s="14"/>
+      <c r="Q3" s="28"/>
+      <c r="R3" s="28"/>
+      <c r="S3" s="28"/>
+      <c r="T3" s="14"/>
+      <c r="U3" s="28"/>
+      <c r="V3" s="13">
         <v>1334511</v>
       </c>
-      <c r="L3" s="13">
-        <v>634511</v>
-      </c>
-      <c r="M3" s="13">
-        <v>56000</v>
-      </c>
-      <c r="N3" s="13">
-        <v>578511</v>
-      </c>
-      <c r="O3" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="P3" s="14">
-        <f t="shared" ref="P3:P21" si="0">L3-M3-N3</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" ht="27" x14ac:dyDescent="0.25">
+      <c r="W3" s="28"/>
+    </row>
+    <row r="4" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
         <v>1001200622</v>
       </c>
@@ -959,26 +1038,33 @@
         <v>1459927.6</v>
       </c>
       <c r="K4" s="13">
+        <v>650000</v>
+      </c>
+      <c r="L4" s="13">
+        <v>56000</v>
+      </c>
+      <c r="M4" s="13">
+        <v>594000</v>
+      </c>
+      <c r="N4" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="O4" s="14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P4" s="14"/>
+      <c r="Q4" s="28"/>
+      <c r="R4" s="28"/>
+      <c r="S4" s="28"/>
+      <c r="T4" s="14"/>
+      <c r="U4" s="28"/>
+      <c r="V4" s="13">
         <v>1250000</v>
       </c>
-      <c r="L4" s="13">
-        <v>650000</v>
-      </c>
-      <c r="M4" s="13">
-        <v>56000</v>
-      </c>
-      <c r="N4" s="13">
-        <v>594000</v>
-      </c>
-      <c r="O4" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="P4" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" ht="27" x14ac:dyDescent="0.25">
+      <c r="W4" s="28"/>
+    </row>
+    <row r="5" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
         <v>1001045472</v>
       </c>
@@ -1006,26 +1092,47 @@
         <v>1559927.6</v>
       </c>
       <c r="K5" s="13">
-        <v>1477558</v>
+        <v>777558</v>
       </c>
       <c r="L5" s="13">
-        <v>777558</v>
+        <v>186726</v>
       </c>
       <c r="M5" s="13">
-        <v>186726</v>
-      </c>
-      <c r="N5" s="13">
         <v>242000</v>
       </c>
-      <c r="O5" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="P5" s="14">
+      <c r="N5" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="O5" s="14">
         <f t="shared" si="0"/>
         <v>348832</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" ht="27" x14ac:dyDescent="0.25">
+      <c r="P5" s="14">
+        <v>1500000</v>
+      </c>
+      <c r="Q5" s="28">
+        <v>0.8</v>
+      </c>
+      <c r="R5" s="28">
+        <v>0.35</v>
+      </c>
+      <c r="S5" s="28">
+        <v>0.4</v>
+      </c>
+      <c r="T5" s="14">
+        <v>7000000</v>
+      </c>
+      <c r="U5" s="28">
+        <v>0.7</v>
+      </c>
+      <c r="V5" s="13">
+        <v>1477558</v>
+      </c>
+      <c r="W5" s="28">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
         <v>80875830</v>
       </c>
@@ -1049,32 +1156,39 @@
       </c>
       <c r="H6" s="21"/>
       <c r="I6" s="22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J6" s="25">
         <v>1489868.18</v>
       </c>
       <c r="K6" s="13">
-        <v>2289070</v>
+        <v>1589070</v>
       </c>
       <c r="L6" s="13">
-        <v>1589070</v>
+        <v>35000</v>
       </c>
       <c r="M6" s="13">
-        <v>35000</v>
-      </c>
-      <c r="N6" s="13">
         <v>612901</v>
       </c>
-      <c r="O6" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="P6" s="14">
+      <c r="N6" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="O6" s="14">
         <f t="shared" si="0"/>
         <v>941169</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="P6" s="14"/>
+      <c r="Q6" s="28"/>
+      <c r="R6" s="28"/>
+      <c r="S6" s="28"/>
+      <c r="T6" s="14"/>
+      <c r="U6" s="28"/>
+      <c r="V6" s="13">
+        <v>2289070</v>
+      </c>
+      <c r="W6" s="28"/>
+    </row>
+    <row r="7" spans="1:23" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
         <v>1006116706</v>
       </c>
@@ -1100,7 +1214,7 @@
         <v>250000</v>
       </c>
       <c r="I7" s="22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J7" s="25">
         <v>643502.2666666666</v>
@@ -1114,16 +1228,23 @@
       <c r="M7" s="13">
         <v>0</v>
       </c>
-      <c r="N7" s="13">
-        <v>0</v>
-      </c>
-      <c r="O7" s="27"/>
-      <c r="P7" s="14">
+      <c r="N7" s="27"/>
+      <c r="O7" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" ht="27" x14ac:dyDescent="0.25">
+      <c r="P7" s="14"/>
+      <c r="Q7" s="28"/>
+      <c r="R7" s="28"/>
+      <c r="S7" s="28"/>
+      <c r="T7" s="14"/>
+      <c r="U7" s="28"/>
+      <c r="V7" s="13">
+        <v>0</v>
+      </c>
+      <c r="W7" s="28"/>
+    </row>
+    <row r="8" spans="1:23" ht="27" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
         <v>1193092448</v>
       </c>
@@ -1151,26 +1272,47 @@
         <v>1559927.6</v>
       </c>
       <c r="K8" s="13">
-        <v>1250000</v>
+        <v>550000</v>
       </c>
       <c r="L8" s="13">
-        <v>550000</v>
+        <v>144726</v>
       </c>
       <c r="M8" s="13">
-        <v>144726</v>
-      </c>
-      <c r="N8" s="13">
         <v>336331</v>
       </c>
-      <c r="O8" s="26" t="s">
-        <v>53</v>
-      </c>
-      <c r="P8" s="14">
+      <c r="N8" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="O8" s="14">
         <f t="shared" si="0"/>
         <v>68943</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="P8" s="14">
+        <v>1555000</v>
+      </c>
+      <c r="Q8" s="28">
+        <v>0.7</v>
+      </c>
+      <c r="R8" s="28">
+        <v>0.34</v>
+      </c>
+      <c r="S8" s="28">
+        <v>0.5</v>
+      </c>
+      <c r="T8" s="14">
+        <v>5000000</v>
+      </c>
+      <c r="U8" s="28">
+        <v>0.5</v>
+      </c>
+      <c r="V8" s="13">
+        <v>1250000</v>
+      </c>
+      <c r="W8" s="28">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
         <v>79910037</v>
       </c>
@@ -1196,30 +1338,37 @@
         <v>353000</v>
       </c>
       <c r="I9" s="22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J9" s="25">
         <v>806927.6</v>
       </c>
       <c r="K9" s="13">
-        <v>0</v>
+        <v>-300000</v>
       </c>
       <c r="L9" s="13">
-        <v>-300000</v>
+        <v>0</v>
       </c>
       <c r="M9" s="13">
         <v>0</v>
       </c>
-      <c r="N9" s="13">
-        <v>0</v>
-      </c>
-      <c r="O9" s="20"/>
-      <c r="P9" s="14">
+      <c r="N9" s="20"/>
+      <c r="O9" s="14">
         <f t="shared" si="0"/>
         <v>-300000</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="P9" s="14"/>
+      <c r="Q9" s="28"/>
+      <c r="R9" s="28"/>
+      <c r="S9" s="28"/>
+      <c r="T9" s="14"/>
+      <c r="U9" s="28"/>
+      <c r="V9" s="13">
+        <v>0</v>
+      </c>
+      <c r="W9" s="28"/>
+    </row>
+    <row r="10" spans="1:23" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
         <v>52767162</v>
       </c>
@@ -1255,16 +1404,23 @@
       <c r="M10" s="13">
         <v>0</v>
       </c>
-      <c r="N10" s="13">
-        <v>0</v>
-      </c>
-      <c r="O10" s="20"/>
-      <c r="P10" s="14">
+      <c r="N10" s="20"/>
+      <c r="O10" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="P10" s="14"/>
+      <c r="Q10" s="28"/>
+      <c r="R10" s="28"/>
+      <c r="S10" s="28"/>
+      <c r="T10" s="14"/>
+      <c r="U10" s="28"/>
+      <c r="V10" s="13">
+        <v>0</v>
+      </c>
+      <c r="W10" s="28"/>
+    </row>
+    <row r="11" spans="1:23" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
         <v>1000795016</v>
       </c>
@@ -1292,24 +1448,31 @@
         <v>1877547.5</v>
       </c>
       <c r="K11" s="13">
-        <v>0</v>
+        <v>226987</v>
       </c>
       <c r="L11" s="13">
-        <v>226987</v>
+        <v>0</v>
       </c>
       <c r="M11" s="13">
         <v>0</v>
       </c>
-      <c r="N11" s="13">
-        <v>0</v>
-      </c>
-      <c r="O11" s="27"/>
-      <c r="P11" s="14">
+      <c r="N11" s="27"/>
+      <c r="O11" s="14">
         <f t="shared" si="0"/>
         <v>226987</v>
       </c>
-    </row>
-    <row r="12" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="P11" s="14"/>
+      <c r="Q11" s="28"/>
+      <c r="R11" s="28"/>
+      <c r="S11" s="28"/>
+      <c r="T11" s="14"/>
+      <c r="U11" s="28"/>
+      <c r="V11" s="13">
+        <v>0</v>
+      </c>
+      <c r="W11" s="28"/>
+    </row>
+    <row r="12" spans="1:23" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
         <v>79593400</v>
       </c>
@@ -1337,24 +1500,31 @@
         <v>8578000</v>
       </c>
       <c r="K12" s="13">
-        <v>0</v>
+        <v>572000</v>
       </c>
       <c r="L12" s="13">
-        <v>572000</v>
+        <v>0</v>
       </c>
       <c r="M12" s="13">
         <v>0</v>
       </c>
-      <c r="N12" s="13">
-        <v>0</v>
-      </c>
-      <c r="O12" s="27"/>
-      <c r="P12" s="14">
+      <c r="N12" s="27"/>
+      <c r="O12" s="14">
         <f t="shared" si="0"/>
         <v>572000</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="P12" s="14"/>
+      <c r="Q12" s="28"/>
+      <c r="R12" s="28"/>
+      <c r="S12" s="28"/>
+      <c r="T12" s="14"/>
+      <c r="U12" s="28"/>
+      <c r="V12" s="13">
+        <v>0</v>
+      </c>
+      <c r="W12" s="28"/>
+    </row>
+    <row r="13" spans="1:23" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
         <v>1023029896</v>
       </c>
@@ -1380,7 +1550,7 @@
         <v>7000</v>
       </c>
       <c r="I13" s="22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J13" s="25">
         <v>952927.6</v>
@@ -1394,16 +1564,37 @@
       <c r="M13" s="13">
         <v>0</v>
       </c>
-      <c r="N13" s="13">
-        <v>0</v>
-      </c>
-      <c r="O13" s="27"/>
+      <c r="N13" s="27"/>
+      <c r="O13" s="14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="P13" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
+        <v>1558800000</v>
+      </c>
+      <c r="Q13" s="28">
+        <v>1</v>
+      </c>
+      <c r="R13" s="28">
+        <v>0.33</v>
+      </c>
+      <c r="S13" s="28">
+        <v>0.3</v>
+      </c>
+      <c r="T13" s="14">
+        <v>7000000</v>
+      </c>
+      <c r="U13" s="28">
+        <v>0.3</v>
+      </c>
+      <c r="V13" s="13">
+        <v>2289070</v>
+      </c>
+      <c r="W13" s="28">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
         <v>1015473856</v>
       </c>
@@ -1427,32 +1618,39 @@
       </c>
       <c r="H14" s="21"/>
       <c r="I14" s="22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J14" s="25">
         <v>1652971.3333333333</v>
       </c>
       <c r="K14" s="13">
-        <v>0</v>
+        <v>24910</v>
       </c>
       <c r="L14" s="13">
-        <v>24910</v>
+        <v>0</v>
       </c>
       <c r="M14" s="13">
         <v>0</v>
       </c>
-      <c r="N14" s="13">
-        <v>0</v>
-      </c>
-      <c r="O14" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="P14" s="14">
+      <c r="N14" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="O14" s="14">
         <f t="shared" si="0"/>
         <v>24910</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="P14" s="14"/>
+      <c r="Q14" s="28"/>
+      <c r="R14" s="28"/>
+      <c r="S14" s="28"/>
+      <c r="T14" s="14"/>
+      <c r="U14" s="28"/>
+      <c r="V14" s="13">
+        <v>0</v>
+      </c>
+      <c r="W14" s="28"/>
+    </row>
+    <row r="15" spans="1:23" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
         <v>1026306646</v>
       </c>
@@ -1478,7 +1676,7 @@
         <v>56000</v>
       </c>
       <c r="I15" s="22" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J15" s="25">
         <v>611639.75333333341</v>
@@ -1492,16 +1690,23 @@
       <c r="M15" s="13">
         <v>0</v>
       </c>
-      <c r="N15" s="13">
-        <v>0</v>
-      </c>
-      <c r="O15" s="27"/>
-      <c r="P15" s="14">
+      <c r="N15" s="27"/>
+      <c r="O15" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="P15" s="14"/>
+      <c r="Q15" s="28"/>
+      <c r="R15" s="28"/>
+      <c r="S15" s="28"/>
+      <c r="T15" s="14"/>
+      <c r="U15" s="28"/>
+      <c r="V15" s="13">
+        <v>0</v>
+      </c>
+      <c r="W15" s="28"/>
+    </row>
+    <row r="16" spans="1:23" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
         <v>1003533086</v>
       </c>
@@ -1527,7 +1732,7 @@
         <v>245400</v>
       </c>
       <c r="I16" s="22" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J16" s="25">
         <v>930894.6</v>
@@ -1541,16 +1746,23 @@
       <c r="M16" s="13">
         <v>0</v>
       </c>
-      <c r="N16" s="13">
-        <v>0</v>
-      </c>
-      <c r="O16" s="27"/>
-      <c r="P16" s="14">
+      <c r="N16" s="27"/>
+      <c r="O16" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="P16" s="14"/>
+      <c r="Q16" s="28"/>
+      <c r="R16" s="28"/>
+      <c r="S16" s="28"/>
+      <c r="T16" s="14"/>
+      <c r="U16" s="28"/>
+      <c r="V16" s="13">
+        <v>0</v>
+      </c>
+      <c r="W16" s="28"/>
+    </row>
+    <row r="17" spans="1:23" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
         <v>1028660836</v>
       </c>
@@ -1576,32 +1788,39 @@
         <v>233166</v>
       </c>
       <c r="I17" s="22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J17" s="25">
         <v>692291.67999999993</v>
       </c>
       <c r="K17" s="13">
-        <v>0</v>
+        <v>335324</v>
       </c>
       <c r="L17" s="13">
+        <v>0</v>
+      </c>
+      <c r="M17" s="13">
         <v>335324</v>
       </c>
-      <c r="M17" s="13">
-        <v>0</v>
-      </c>
-      <c r="N17" s="13">
-        <v>335324</v>
-      </c>
-      <c r="O17" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="P17" s="14">
+      <c r="N17" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="O17" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="P17" s="14"/>
+      <c r="Q17" s="28"/>
+      <c r="R17" s="28"/>
+      <c r="S17" s="28"/>
+      <c r="T17" s="14"/>
+      <c r="U17" s="28"/>
+      <c r="V17" s="13">
+        <v>0</v>
+      </c>
+      <c r="W17" s="28"/>
+    </row>
+    <row r="18" spans="1:23" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
         <v>1053330769</v>
       </c>
@@ -1627,7 +1846,7 @@
         <v>59000</v>
       </c>
       <c r="I18" s="23" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J18" s="25">
         <v>1078063.5133333334</v>
@@ -1641,21 +1860,28 @@
       <c r="M18" s="13">
         <v>0</v>
       </c>
-      <c r="N18" s="13">
-        <v>0</v>
-      </c>
-      <c r="O18" s="27"/>
-      <c r="P18" s="14">
+      <c r="N18" s="27"/>
+      <c r="O18" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="P18" s="14"/>
+      <c r="Q18" s="28"/>
+      <c r="R18" s="28"/>
+      <c r="S18" s="28"/>
+      <c r="T18" s="14"/>
+      <c r="U18" s="28"/>
+      <c r="V18" s="13">
+        <v>0</v>
+      </c>
+      <c r="W18" s="28"/>
+    </row>
+    <row r="19" spans="1:23" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A19" s="11">
         <v>1013673759</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C19" s="4">
         <v>875452.5</v>
@@ -1678,31 +1904,38 @@
         <v>859927.6</v>
       </c>
       <c r="K19" s="13">
-        <v>0</v>
+        <v>519510</v>
       </c>
       <c r="L19" s="13">
-        <v>519510</v>
+        <v>35000</v>
       </c>
       <c r="M19" s="13">
-        <v>35000</v>
-      </c>
-      <c r="N19" s="13">
         <v>100000</v>
       </c>
-      <c r="O19" s="27" t="s">
-        <v>56</v>
-      </c>
-      <c r="P19" s="14">
+      <c r="N19" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="O19" s="14">
         <f t="shared" si="0"/>
         <v>384510</v>
       </c>
-    </row>
-    <row r="20" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="P19" s="14"/>
+      <c r="Q19" s="28"/>
+      <c r="R19" s="28"/>
+      <c r="S19" s="28"/>
+      <c r="T19" s="14"/>
+      <c r="U19" s="28"/>
+      <c r="V19" s="13">
+        <v>0</v>
+      </c>
+      <c r="W19" s="28"/>
+    </row>
+    <row r="20" spans="1:23" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
         <v>1003483344</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C20" s="4">
         <v>875452.5</v>
@@ -1723,7 +1956,7 @@
         <v>56000</v>
       </c>
       <c r="I20" s="23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J20" s="25">
         <v>1118333.6000000001</v>
@@ -1737,21 +1970,28 @@
       <c r="M20" s="13">
         <v>0</v>
       </c>
-      <c r="N20" s="13">
-        <v>0</v>
-      </c>
-      <c r="O20" s="27"/>
-      <c r="P20" s="14">
+      <c r="N20" s="27"/>
+      <c r="O20" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="P20" s="14"/>
+      <c r="Q20" s="28"/>
+      <c r="R20" s="28"/>
+      <c r="S20" s="28"/>
+      <c r="T20" s="14"/>
+      <c r="U20" s="28"/>
+      <c r="V20" s="13">
+        <v>0</v>
+      </c>
+      <c r="W20" s="28"/>
+    </row>
+    <row r="21" spans="1:23" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
         <v>1119210446</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C21" s="4">
         <v>817089</v>
@@ -1772,32 +2012,39 @@
         <v>7000</v>
       </c>
       <c r="I21" s="23" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J21" s="25">
         <v>1032880.2133333335</v>
       </c>
       <c r="K21" s="13">
-        <v>0</v>
+        <v>66666.666666666672</v>
       </c>
       <c r="L21" s="13">
-        <v>66666.666666666672</v>
+        <v>0</v>
       </c>
       <c r="M21" s="13">
         <v>0</v>
       </c>
-      <c r="N21" s="13">
-        <v>0</v>
-      </c>
-      <c r="O21" s="27" t="s">
-        <v>57</v>
-      </c>
-      <c r="P21" s="14">
+      <c r="N21" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="O21" s="14">
         <f t="shared" si="0"/>
         <v>66666.666666666672</v>
       </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P21" s="14"/>
+      <c r="Q21" s="28"/>
+      <c r="R21" s="28"/>
+      <c r="S21" s="28"/>
+      <c r="T21" s="14"/>
+      <c r="U21" s="28"/>
+      <c r="V21" s="13">
+        <v>0</v>
+      </c>
+      <c r="W21" s="28"/>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A22" s="11"/>
       <c r="B22" s="12"/>
       <c r="C22" s="4"/>
@@ -1810,10 +2057,17 @@
       <c r="J22" s="13"/>
       <c r="K22" s="13"/>
       <c r="L22" s="13"/>
-      <c r="M22" s="13"/>
+      <c r="M22" s="15"/>
       <c r="N22" s="15"/>
       <c r="O22" s="15"/>
       <c r="P22" s="15"/>
+      <c r="Q22" s="28"/>
+      <c r="R22" s="28"/>
+      <c r="S22" s="28"/>
+      <c r="T22" s="15"/>
+      <c r="U22" s="28"/>
+      <c r="V22" s="13"/>
+      <c r="W22" s="28"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/empleados.xlsx
+++ b/empleados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\NOMINA Y RRHH\NOMINA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82092603-9660-4E23-AE92-9BBB33E4BCE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{339FF95F-FB88-4C95-8074-0460E7845E27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DA975529-9E83-4FFA-BD35-5CA808A15280}"/>
   </bookViews>
@@ -227,10 +227,10 @@
     <t>PORCENTAJE CARTERA</t>
   </si>
   <si>
-    <t>PORCENTAJE COMISION</t>
-  </si>
-  <si>
     <t>COMISION TOTAL</t>
+  </si>
+  <si>
+    <t>PORCENTAJE TOTAL</t>
   </si>
 </sst>
 </file>
@@ -821,7 +821,7 @@
     <col min="20" max="20" width="15.85546875" style="10" customWidth="1"/>
     <col min="21" max="21" width="18.7109375" style="10" customWidth="1"/>
     <col min="22" max="22" width="15.85546875" style="18" customWidth="1"/>
-    <col min="23" max="23" width="20.140625" style="10" customWidth="1"/>
+    <col min="23" max="23" width="16.7109375" style="10" customWidth="1"/>
     <col min="24" max="16384" width="11.42578125" style="10"/>
   </cols>
   <sheetData>
@@ -890,10 +890,10 @@
         <v>62</v>
       </c>
       <c r="V1" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="W1" s="8" t="s">
         <v>64</v>
-      </c>
-      <c r="W1" s="8" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:23" ht="16.5" x14ac:dyDescent="0.25">

--- a/empleados.xlsx
+++ b/empleados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\NOMINA Y RRHH\NOMINA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{339FF95F-FB88-4C95-8074-0460E7845E27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F9C8EE9-AC58-42F0-BC44-B345FF2F7F95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DA975529-9E83-4FFA-BD35-5CA808A15280}"/>
   </bookViews>
@@ -455,7 +455,7 @@
     <xf numFmtId="166" fontId="6" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1111,25 +1111,25 @@
         <v>1500000</v>
       </c>
       <c r="Q5" s="28">
-        <v>0.8</v>
+        <v>80</v>
       </c>
       <c r="R5" s="28">
-        <v>0.35</v>
+        <v>35</v>
       </c>
       <c r="S5" s="28">
-        <v>0.4</v>
+        <v>80</v>
       </c>
       <c r="T5" s="14">
         <v>7000000</v>
       </c>
       <c r="U5" s="28">
-        <v>0.7</v>
+        <v>70</v>
       </c>
       <c r="V5" s="13">
         <v>1477558</v>
       </c>
       <c r="W5" s="28">
-        <v>0.9</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:23" ht="27" x14ac:dyDescent="0.25">
@@ -1291,25 +1291,25 @@
         <v>1555000</v>
       </c>
       <c r="Q8" s="28">
-        <v>0.7</v>
+        <v>100</v>
       </c>
       <c r="R8" s="28">
-        <v>0.34</v>
+        <v>34</v>
       </c>
       <c r="S8" s="28">
-        <v>0.5</v>
+        <v>90</v>
       </c>
       <c r="T8" s="14">
         <v>5000000</v>
       </c>
       <c r="U8" s="28">
-        <v>0.5</v>
+        <v>50</v>
       </c>
       <c r="V8" s="13">
         <v>1250000</v>
       </c>
       <c r="W8" s="28">
-        <v>0.3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:23" ht="16.5" x14ac:dyDescent="0.25">
@@ -1573,25 +1573,25 @@
         <v>1558800000</v>
       </c>
       <c r="Q13" s="28">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="R13" s="28">
-        <v>0.33</v>
+        <v>33</v>
       </c>
       <c r="S13" s="28">
-        <v>0.3</v>
+        <v>75</v>
       </c>
       <c r="T13" s="14">
         <v>7000000</v>
       </c>
       <c r="U13" s="28">
-        <v>0.3</v>
+        <v>30</v>
       </c>
       <c r="V13" s="13">
         <v>2289070</v>
       </c>
       <c r="W13" s="28">
-        <v>0.8</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:23" ht="16.5" x14ac:dyDescent="0.25">

--- a/empleados.xlsx
+++ b/empleados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\NOMINA Y RRHH\NOMINA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F9C8EE9-AC58-42F0-BC44-B345FF2F7F95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C53A8D10-9D39-4D46-8A5A-939E63F8D274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DA975529-9E83-4FFA-BD35-5CA808A15280}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="64">
   <si>
     <t>CEDULA</t>
   </si>
@@ -101,9 +101,6 @@
     <t>TRIVIÑO RIOS JOSE JULIAN</t>
   </si>
   <si>
-    <t>CAMACHO ABRIL SANDRA MILENA</t>
-  </si>
-  <si>
     <t>ALVAREZ ESCOBAR JUAN ESTEBAN</t>
   </si>
   <si>
@@ -116,9 +113,6 @@
     <t>ALVAREZ ESCOBAR NICOLAS ENRIQUE</t>
   </si>
   <si>
-    <t>RAMIREZ VARGAS SANTIAGO ANDRES</t>
-  </si>
-  <si>
     <t>SUAREZ ORTIZ DANNY ALEJANDRO</t>
   </si>
   <si>
@@ -140,9 +134,6 @@
     <t>MICHEL STEVEN HERNANDEZ ROJAS</t>
   </si>
   <si>
-    <t>OSWALDO DUCUARA  VERA</t>
-  </si>
-  <si>
     <t>360,000 vales</t>
   </si>
   <si>
@@ -164,9 +155,6 @@
     <t>3 Dias incap</t>
   </si>
   <si>
-    <t>3 dias incap + renuncia 26 de Agos+56,000 (8) Caritas</t>
-  </si>
-  <si>
     <t>203,400 Prestamo+42,000 (6) Caritas</t>
   </si>
   <si>
@@ -179,9 +167,6 @@
     <t>56,000 (8) Caritas</t>
   </si>
   <si>
-    <t>Ing 17 Sep+7,000 (1) carita</t>
-  </si>
-  <si>
     <t>276,350 Prestamo+56,000 (8) Caritas+10,000 sugeridos+292,161 VALES</t>
   </si>
   <si>
@@ -206,9 +191,6 @@
     <t>100,000 VALES+35,000 (5) Caritas</t>
   </si>
   <si>
-    <t>PAGO 16 DE SEPTIEMBRE POR NO AFILIACION</t>
-  </si>
-  <si>
     <t>VENTAS TOTALES</t>
   </si>
   <si>
@@ -231,6 +213,21 @@
   </si>
   <si>
     <t>PORCENTAJE TOTAL</t>
+  </si>
+  <si>
+    <t>VENTAS MAYOR</t>
+  </si>
+  <si>
+    <t>VENTAS CALLE</t>
+  </si>
+  <si>
+    <t>COMISION MAYOR</t>
+  </si>
+  <si>
+    <t>COMISION CALLE</t>
+  </si>
+  <si>
+    <t>COMISION VENTAS</t>
   </si>
 </sst>
 </file>
@@ -797,7 +794,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E263F044-EB2C-4A38-BF1B-A61CE6B829F6}">
-  <dimension ref="A1:W22"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.140625" style="16" customWidth="1"/>
@@ -821,11 +818,16 @@
     <col min="20" max="20" width="15.85546875" style="10" customWidth="1"/>
     <col min="21" max="21" width="18.7109375" style="10" customWidth="1"/>
     <col min="22" max="22" width="15.85546875" style="18" customWidth="1"/>
-    <col min="23" max="23" width="16.7109375" style="10" customWidth="1"/>
-    <col min="24" max="16384" width="11.42578125" style="10"/>
+    <col min="23" max="24" width="16.7109375" style="10" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="10" customWidth="1"/>
+    <col min="26" max="26" width="17.28515625" style="10" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="10" customWidth="1"/>
+    <col min="28" max="28" width="15.7109375" style="10" customWidth="1"/>
+    <col min="29" max="29" width="16.140625" style="10" customWidth="1"/>
+    <col min="30" max="16384" width="11.42578125" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" ht="27" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -863,40 +865,58 @@
         <v>11</v>
       </c>
       <c r="M1" s="9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="N1" s="9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="O1" s="9" t="s">
         <v>12</v>
       </c>
       <c r="P1" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q1" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="R1" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="S1" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="T1" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="U1" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="V1" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="W1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="X1" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA1" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="R1" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="S1" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="T1" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="U1" s="9" t="s">
+      <c r="AB1" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="V1" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="W1" s="8" t="s">
-        <v>64</v>
+      <c r="AC1" s="8" t="s">
+        <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A2" s="11">
         <v>52114146</v>
       </c>
@@ -922,7 +942,7 @@
         <v>360000</v>
       </c>
       <c r="I2" s="22" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J2" s="24">
         <v>3000000.0000000005</v>
@@ -951,8 +971,14 @@
         <v>0</v>
       </c>
       <c r="W2" s="28"/>
+      <c r="X2" s="13"/>
+      <c r="Y2" s="13"/>
+      <c r="Z2" s="13"/>
+      <c r="AA2" s="13"/>
+      <c r="AB2" s="13"/>
+      <c r="AC2" s="13"/>
     </row>
-    <row r="3" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" ht="27" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
         <v>94288721</v>
       </c>
@@ -978,7 +1004,7 @@
         <v>29871</v>
       </c>
       <c r="I3" s="22" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="J3" s="25">
         <v>1530056.6</v>
@@ -993,10 +1019,10 @@
         <v>578511</v>
       </c>
       <c r="N3" s="20" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="O3" s="14">
-        <f t="shared" ref="O3:O21" si="0">K3-L3-M3</f>
+        <f t="shared" ref="O3:O18" si="0">K3-L3-M3</f>
         <v>0</v>
       </c>
       <c r="P3" s="14"/>
@@ -1006,11 +1032,17 @@
       <c r="T3" s="14"/>
       <c r="U3" s="28"/>
       <c r="V3" s="13">
-        <v>1334511</v>
+        <v>0</v>
       </c>
       <c r="W3" s="28"/>
+      <c r="X3" s="13"/>
+      <c r="Y3" s="13"/>
+      <c r="Z3" s="13"/>
+      <c r="AA3" s="13"/>
+      <c r="AB3" s="13"/>
+      <c r="AC3" s="13"/>
     </row>
-    <row r="4" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" ht="27" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
         <v>1001200622</v>
       </c>
@@ -1047,7 +1079,7 @@
         <v>594000</v>
       </c>
       <c r="N4" s="26" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="O4" s="14">
         <f t="shared" si="0"/>
@@ -1060,11 +1092,17 @@
       <c r="T4" s="14"/>
       <c r="U4" s="28"/>
       <c r="V4" s="13">
-        <v>1250000</v>
+        <v>0</v>
       </c>
       <c r="W4" s="28"/>
+      <c r="X4" s="13"/>
+      <c r="Y4" s="13"/>
+      <c r="Z4" s="13"/>
+      <c r="AA4" s="13"/>
+      <c r="AB4" s="13"/>
+      <c r="AC4" s="13"/>
     </row>
-    <row r="5" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" ht="27" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
         <v>1001045472</v>
       </c>
@@ -1101,38 +1139,44 @@
         <v>242000</v>
       </c>
       <c r="N5" s="20" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="O5" s="14">
         <f t="shared" si="0"/>
         <v>348832</v>
       </c>
       <c r="P5" s="14">
+        <v>123456789</v>
+      </c>
+      <c r="Q5" s="28"/>
+      <c r="R5" s="28"/>
+      <c r="S5" s="28"/>
+      <c r="T5" s="14"/>
+      <c r="U5" s="28"/>
+      <c r="V5" s="13">
+        <v>0</v>
+      </c>
+      <c r="W5" s="28"/>
+      <c r="X5" s="13">
         <v>1500000</v>
       </c>
-      <c r="Q5" s="28">
-        <v>80</v>
-      </c>
-      <c r="R5" s="28">
-        <v>35</v>
-      </c>
-      <c r="S5" s="28">
-        <v>80</v>
-      </c>
-      <c r="T5" s="14">
-        <v>7000000</v>
-      </c>
-      <c r="U5" s="28">
-        <v>70</v>
-      </c>
-      <c r="V5" s="13">
-        <v>1477558</v>
-      </c>
-      <c r="W5" s="28">
-        <v>90</v>
+      <c r="Y5" s="13">
+        <v>123456789</v>
+      </c>
+      <c r="Z5" s="13">
+        <v>1500000</v>
+      </c>
+      <c r="AA5" s="13">
+        <v>123456789</v>
+      </c>
+      <c r="AB5" s="13">
+        <v>1500000</v>
+      </c>
+      <c r="AC5" s="13">
+        <v>3000000</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" ht="27" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
         <v>80875830</v>
       </c>
@@ -1156,7 +1200,7 @@
       </c>
       <c r="H6" s="21"/>
       <c r="I6" s="22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="J6" s="25">
         <v>1489868.18</v>
@@ -1171,7 +1215,7 @@
         <v>612901</v>
       </c>
       <c r="N6" s="20" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="O6" s="14">
         <f t="shared" si="0"/>
@@ -1184,11 +1228,17 @@
       <c r="T6" s="14"/>
       <c r="U6" s="28"/>
       <c r="V6" s="13">
-        <v>2289070</v>
+        <v>0</v>
       </c>
       <c r="W6" s="28"/>
+      <c r="X6" s="13"/>
+      <c r="Y6" s="13"/>
+      <c r="Z6" s="13"/>
+      <c r="AA6" s="13"/>
+      <c r="AB6" s="13"/>
+      <c r="AC6" s="13"/>
     </row>
-    <row r="7" spans="1:23" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
         <v>1006116706</v>
       </c>
@@ -1214,7 +1264,7 @@
         <v>250000</v>
       </c>
       <c r="I7" s="22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="J7" s="25">
         <v>643502.2666666666</v>
@@ -1243,8 +1293,14 @@
         <v>0</v>
       </c>
       <c r="W7" s="28"/>
+      <c r="X7" s="13"/>
+      <c r="Y7" s="13"/>
+      <c r="Z7" s="13"/>
+      <c r="AA7" s="13"/>
+      <c r="AB7" s="13"/>
+      <c r="AC7" s="13"/>
     </row>
-    <row r="8" spans="1:23" ht="27" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" ht="27" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
         <v>1193092448</v>
       </c>
@@ -1281,38 +1337,30 @@
         <v>336331</v>
       </c>
       <c r="N8" s="26" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="O8" s="14">
         <f t="shared" si="0"/>
         <v>68943</v>
       </c>
-      <c r="P8" s="14">
-        <v>1555000</v>
-      </c>
-      <c r="Q8" s="28">
-        <v>100</v>
-      </c>
-      <c r="R8" s="28">
-        <v>34</v>
-      </c>
-      <c r="S8" s="28">
-        <v>90</v>
-      </c>
-      <c r="T8" s="14">
-        <v>5000000</v>
-      </c>
-      <c r="U8" s="28">
-        <v>50</v>
-      </c>
+      <c r="P8" s="14"/>
+      <c r="Q8" s="28"/>
+      <c r="R8" s="28"/>
+      <c r="S8" s="28"/>
+      <c r="T8" s="14"/>
+      <c r="U8" s="28"/>
       <c r="V8" s="13">
-        <v>1250000</v>
-      </c>
-      <c r="W8" s="28">
-        <v>30</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W8" s="28"/>
+      <c r="X8" s="13"/>
+      <c r="Y8" s="13"/>
+      <c r="Z8" s="13"/>
+      <c r="AA8" s="13"/>
+      <c r="AB8" s="13"/>
+      <c r="AC8" s="13"/>
     </row>
-    <row r="9" spans="1:23" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
         <v>79910037</v>
       </c>
@@ -1338,7 +1386,7 @@
         <v>353000</v>
       </c>
       <c r="I9" s="22" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="J9" s="25">
         <v>806927.6</v>
@@ -1367,33 +1415,39 @@
         <v>0</v>
       </c>
       <c r="W9" s="28"/>
+      <c r="X9" s="13"/>
+      <c r="Y9" s="13"/>
+      <c r="Z9" s="13"/>
+      <c r="AA9" s="13"/>
+      <c r="AB9" s="13"/>
+      <c r="AC9" s="13"/>
     </row>
-    <row r="10" spans="1:23" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
-        <v>52767162</v>
+        <v>1000795016</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C10" s="4">
-        <v>0</v>
+        <v>1075000</v>
       </c>
       <c r="D10" s="5">
-        <v>0</v>
+        <v>124547.49999999999</v>
       </c>
       <c r="E10" s="13">
         <v>0</v>
       </c>
       <c r="F10" s="13">
-        <v>0</v>
+        <v>172000</v>
       </c>
       <c r="G10" s="13">
-        <v>0</v>
+        <v>850000</v>
       </c>
       <c r="H10" s="21"/>
       <c r="I10" s="22"/>
       <c r="J10" s="25">
-        <v>0</v>
+        <v>1877547.5</v>
       </c>
       <c r="K10" s="13">
         <v>0</v>
@@ -1404,7 +1458,7 @@
       <c r="M10" s="13">
         <v>0</v>
       </c>
-      <c r="N10" s="20"/>
+      <c r="N10" s="27"/>
       <c r="O10" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1419,36 +1473,42 @@
         <v>0</v>
       </c>
       <c r="W10" s="28"/>
+      <c r="X10" s="13"/>
+      <c r="Y10" s="13"/>
+      <c r="Z10" s="13"/>
+      <c r="AA10" s="13"/>
+      <c r="AB10" s="13"/>
+      <c r="AC10" s="13"/>
     </row>
-    <row r="11" spans="1:23" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
-        <v>1000795016</v>
+        <v>79593400</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>22</v>
       </c>
       <c r="C11" s="4">
-        <v>1075000</v>
+        <v>7150000</v>
       </c>
       <c r="D11" s="5">
-        <v>124547.49999999999</v>
+        <v>0</v>
       </c>
       <c r="E11" s="13">
         <v>0</v>
       </c>
       <c r="F11" s="13">
-        <v>172000</v>
+        <v>572000</v>
       </c>
       <c r="G11" s="13">
-        <v>850000</v>
+        <v>2000000</v>
       </c>
       <c r="H11" s="21"/>
       <c r="I11" s="22"/>
       <c r="J11" s="25">
-        <v>1877547.5</v>
+        <v>8578000</v>
       </c>
       <c r="K11" s="13">
-        <v>226987</v>
+        <v>572000</v>
       </c>
       <c r="L11" s="13">
         <v>0</v>
@@ -1459,7 +1519,7 @@
       <c r="N11" s="27"/>
       <c r="O11" s="14">
         <f t="shared" si="0"/>
-        <v>226987</v>
+        <v>572000</v>
       </c>
       <c r="P11" s="14"/>
       <c r="Q11" s="28"/>
@@ -1471,36 +1531,46 @@
         <v>0</v>
       </c>
       <c r="W11" s="28"/>
+      <c r="X11" s="13"/>
+      <c r="Y11" s="13"/>
+      <c r="Z11" s="13"/>
+      <c r="AA11" s="13"/>
+      <c r="AB11" s="13"/>
+      <c r="AC11" s="13"/>
     </row>
-    <row r="12" spans="1:23" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
-        <v>79593400</v>
+        <v>1023029896</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>23</v>
       </c>
       <c r="C12" s="4">
-        <v>7150000</v>
+        <v>875452.5</v>
       </c>
       <c r="D12" s="5">
-        <v>0</v>
+        <v>124547.49999999999</v>
       </c>
       <c r="E12" s="13">
         <v>0</v>
       </c>
       <c r="F12" s="13">
-        <v>572000</v>
+        <v>140072.4</v>
       </c>
       <c r="G12" s="13">
-        <v>2000000</v>
-      </c>
-      <c r="H12" s="21"/>
-      <c r="I12" s="22"/>
+        <v>100000</v>
+      </c>
+      <c r="H12" s="21">
+        <v>7000</v>
+      </c>
+      <c r="I12" s="22" t="s">
+        <v>37</v>
+      </c>
       <c r="J12" s="25">
-        <v>8578000</v>
+        <v>952927.6</v>
       </c>
       <c r="K12" s="13">
-        <v>572000</v>
+        <v>0</v>
       </c>
       <c r="L12" s="13">
         <v>0</v>
@@ -1511,7 +1581,7 @@
       <c r="N12" s="27"/>
       <c r="O12" s="14">
         <f t="shared" si="0"/>
-        <v>572000</v>
+        <v>0</v>
       </c>
       <c r="P12" s="14"/>
       <c r="Q12" s="28"/>
@@ -1523,37 +1593,41 @@
         <v>0</v>
       </c>
       <c r="W12" s="28"/>
+      <c r="X12" s="13"/>
+      <c r="Y12" s="13"/>
+      <c r="Z12" s="13"/>
+      <c r="AA12" s="13"/>
+      <c r="AB12" s="13"/>
+      <c r="AC12" s="13"/>
     </row>
-    <row r="13" spans="1:23" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
-        <v>1023029896</v>
+        <v>1015473856</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>24</v>
       </c>
       <c r="C13" s="4">
-        <v>875452.5</v>
+        <v>1100000</v>
       </c>
       <c r="D13" s="5">
-        <v>124547.49999999999</v>
+        <v>99638</v>
       </c>
       <c r="E13" s="13">
         <v>0</v>
       </c>
       <c r="F13" s="13">
-        <v>140072.4</v>
+        <v>146666.66666666666</v>
       </c>
       <c r="G13" s="13">
-        <v>100000</v>
-      </c>
-      <c r="H13" s="21">
-        <v>7000</v>
-      </c>
+        <v>600000</v>
+      </c>
+      <c r="H13" s="21"/>
       <c r="I13" s="22" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J13" s="25">
-        <v>952927.6</v>
+        <v>1652971.3333333333</v>
       </c>
       <c r="K13" s="13">
         <v>0</v>
@@ -1564,67 +1638,63 @@
       <c r="M13" s="13">
         <v>0</v>
       </c>
-      <c r="N13" s="27"/>
+      <c r="N13" s="27" t="s">
+        <v>48</v>
+      </c>
       <c r="O13" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P13" s="14">
-        <v>1558800000</v>
-      </c>
-      <c r="Q13" s="28">
-        <v>100</v>
-      </c>
-      <c r="R13" s="28">
-        <v>33</v>
-      </c>
-      <c r="S13" s="28">
-        <v>75</v>
-      </c>
-      <c r="T13" s="14">
-        <v>7000000</v>
-      </c>
-      <c r="U13" s="28">
-        <v>30</v>
-      </c>
+      <c r="P13" s="14"/>
+      <c r="Q13" s="28"/>
+      <c r="R13" s="28"/>
+      <c r="S13" s="28"/>
+      <c r="T13" s="14"/>
+      <c r="U13" s="28"/>
       <c r="V13" s="13">
-        <v>2289070</v>
-      </c>
-      <c r="W13" s="28">
-        <v>80</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W13" s="28"/>
+      <c r="X13" s="13"/>
+      <c r="Y13" s="13"/>
+      <c r="Z13" s="13"/>
+      <c r="AA13" s="13"/>
+      <c r="AB13" s="13"/>
+      <c r="AC13" s="13"/>
     </row>
-    <row r="14" spans="1:23" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
-        <v>1015473856</v>
+        <v>1003533086</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>25</v>
       </c>
       <c r="C14" s="4">
-        <v>1100000</v>
+        <v>875452.5</v>
       </c>
       <c r="D14" s="5">
-        <v>99638</v>
+        <v>124547.49999999999</v>
       </c>
       <c r="E14" s="13">
-        <v>0</v>
+        <v>316367</v>
       </c>
       <c r="F14" s="13">
-        <v>146666.66666666666</v>
+        <v>140072.4</v>
       </c>
       <c r="G14" s="13">
-        <v>600000</v>
-      </c>
-      <c r="H14" s="21"/>
+        <v>0</v>
+      </c>
+      <c r="H14" s="21">
+        <v>245400</v>
+      </c>
       <c r="I14" s="22" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J14" s="25">
-        <v>1652971.3333333333</v>
+        <v>930894.6</v>
       </c>
       <c r="K14" s="13">
-        <v>24910</v>
+        <v>0</v>
       </c>
       <c r="L14" s="13">
         <v>0</v>
@@ -1632,12 +1702,10 @@
       <c r="M14" s="13">
         <v>0</v>
       </c>
-      <c r="N14" s="27" t="s">
-        <v>53</v>
-      </c>
+      <c r="N14" s="27"/>
       <c r="O14" s="14">
         <f t="shared" si="0"/>
-        <v>24910</v>
+        <v>0</v>
       </c>
       <c r="P14" s="14"/>
       <c r="Q14" s="28"/>
@@ -1649,48 +1717,56 @@
         <v>0</v>
       </c>
       <c r="W14" s="28"/>
+      <c r="X14" s="13"/>
+      <c r="Y14" s="13"/>
+      <c r="Z14" s="13"/>
+      <c r="AA14" s="13"/>
+      <c r="AB14" s="13"/>
+      <c r="AC14" s="13"/>
     </row>
-    <row r="15" spans="1:23" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
-        <v>1026306646</v>
+        <v>1028660836</v>
       </c>
       <c r="B15" s="12" t="s">
         <v>26</v>
       </c>
       <c r="C15" s="4">
-        <v>641998.5</v>
+        <v>875452.5</v>
       </c>
       <c r="D15" s="5">
-        <v>66425.333333333328</v>
+        <v>124547.49999999999</v>
       </c>
       <c r="E15" s="13">
-        <v>80612</v>
+        <v>60861</v>
       </c>
       <c r="F15" s="13">
-        <v>121396.08</v>
+        <v>135403.32</v>
       </c>
       <c r="G15" s="13">
         <v>0</v>
       </c>
       <c r="H15" s="21">
-        <v>56000</v>
+        <v>233166</v>
       </c>
       <c r="I15" s="22" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J15" s="25">
-        <v>611639.75333333341</v>
+        <v>692291.67999999993</v>
       </c>
       <c r="K15" s="13">
-        <v>0</v>
+        <v>335324</v>
       </c>
       <c r="L15" s="13">
         <v>0</v>
       </c>
       <c r="M15" s="13">
-        <v>0</v>
-      </c>
-      <c r="N15" s="27"/>
+        <v>335324</v>
+      </c>
+      <c r="N15" s="27" t="s">
+        <v>49</v>
+      </c>
       <c r="O15" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1705,10 +1781,16 @@
         <v>0</v>
       </c>
       <c r="W15" s="28"/>
+      <c r="X15" s="13"/>
+      <c r="Y15" s="13"/>
+      <c r="Z15" s="13"/>
+      <c r="AA15" s="13"/>
+      <c r="AB15" s="13"/>
+      <c r="AC15" s="13"/>
     </row>
-    <row r="16" spans="1:23" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
-        <v>1003533086</v>
+        <v>1053330769</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>27</v>
@@ -1717,25 +1799,25 @@
         <v>875452.5</v>
       </c>
       <c r="D16" s="5">
-        <v>124547.49999999999</v>
+        <v>116244.33333333333</v>
       </c>
       <c r="E16" s="13">
-        <v>316367</v>
+        <v>280770</v>
       </c>
       <c r="F16" s="13">
-        <v>140072.4</v>
+        <v>135403.32</v>
       </c>
       <c r="G16" s="13">
         <v>0</v>
       </c>
       <c r="H16" s="21">
-        <v>245400</v>
-      </c>
-      <c r="I16" s="22" t="s">
-        <v>43</v>
+        <v>59000</v>
+      </c>
+      <c r="I16" s="23" t="s">
+        <v>41</v>
       </c>
       <c r="J16" s="25">
-        <v>930894.6</v>
+        <v>1078063.5133333334</v>
       </c>
       <c r="K16" s="13">
         <v>0</v>
@@ -1761,13 +1843,19 @@
         <v>0</v>
       </c>
       <c r="W16" s="28"/>
+      <c r="X16" s="13"/>
+      <c r="Y16" s="13"/>
+      <c r="Z16" s="13"/>
+      <c r="AA16" s="13"/>
+      <c r="AB16" s="13"/>
+      <c r="AC16" s="13"/>
     </row>
-    <row r="17" spans="1:23" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:29" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
-        <v>1028660836</v>
+        <v>1013673759</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C17" s="4">
         <v>875452.5</v>
@@ -1776,38 +1864,34 @@
         <v>124547.49999999999</v>
       </c>
       <c r="E17" s="13">
-        <v>60861</v>
+        <v>0</v>
       </c>
       <c r="F17" s="13">
-        <v>135403.32</v>
+        <v>140072.4</v>
       </c>
       <c r="G17" s="13">
         <v>0</v>
       </c>
-      <c r="H17" s="21">
-        <v>233166</v>
-      </c>
-      <c r="I17" s="22" t="s">
-        <v>44</v>
-      </c>
+      <c r="H17" s="21"/>
+      <c r="I17" s="23"/>
       <c r="J17" s="25">
-        <v>692291.67999999993</v>
+        <v>859927.6</v>
       </c>
       <c r="K17" s="13">
-        <v>335324</v>
+        <v>519510</v>
       </c>
       <c r="L17" s="13">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="M17" s="13">
-        <v>335324</v>
+        <v>100000</v>
       </c>
       <c r="N17" s="27" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="O17" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>384510</v>
       </c>
       <c r="P17" s="14"/>
       <c r="Q17" s="28"/>
@@ -1819,37 +1903,43 @@
         <v>0</v>
       </c>
       <c r="W17" s="28"/>
+      <c r="X17" s="13"/>
+      <c r="Y17" s="13"/>
+      <c r="Z17" s="13"/>
+      <c r="AA17" s="13"/>
+      <c r="AB17" s="13"/>
+      <c r="AC17" s="13"/>
     </row>
-    <row r="18" spans="1:23" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:29" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
-        <v>1053330769</v>
+        <v>1003483344</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C18" s="4">
         <v>875452.5</v>
       </c>
       <c r="D18" s="5">
-        <v>116244.33333333333</v>
+        <v>124547.49999999999</v>
       </c>
       <c r="E18" s="13">
-        <v>280770</v>
+        <v>314406</v>
       </c>
       <c r="F18" s="13">
-        <v>135403.32</v>
+        <v>140072.4</v>
       </c>
       <c r="G18" s="13">
         <v>0</v>
       </c>
       <c r="H18" s="21">
-        <v>59000</v>
+        <v>56000</v>
       </c>
       <c r="I18" s="23" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J18" s="25">
-        <v>1078063.5133333334</v>
+        <v>1118333.6000000001</v>
       </c>
       <c r="K18" s="13">
         <v>0</v>
@@ -1875,199 +1965,43 @@
         <v>0</v>
       </c>
       <c r="W18" s="28"/>
+      <c r="X18" s="13"/>
+      <c r="Y18" s="13"/>
+      <c r="Z18" s="13"/>
+      <c r="AA18" s="13"/>
+      <c r="AB18" s="13"/>
+      <c r="AC18" s="13"/>
     </row>
-    <row r="19" spans="1:23" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="11">
-        <v>1013673759</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="C19" s="4">
-        <v>875452.5</v>
-      </c>
-      <c r="D19" s="5">
-        <v>124547.49999999999</v>
-      </c>
-      <c r="E19" s="13">
-        <v>0</v>
-      </c>
-      <c r="F19" s="13">
-        <v>140072.4</v>
-      </c>
-      <c r="G19" s="13">
-        <v>0</v>
-      </c>
-      <c r="H19" s="21"/>
-      <c r="I19" s="23"/>
-      <c r="J19" s="25">
-        <v>859927.6</v>
-      </c>
-      <c r="K19" s="13">
-        <v>519510</v>
-      </c>
-      <c r="L19" s="13">
-        <v>35000</v>
-      </c>
-      <c r="M19" s="13">
-        <v>100000</v>
-      </c>
-      <c r="N19" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="O19" s="14">
-        <f t="shared" si="0"/>
-        <v>384510</v>
-      </c>
-      <c r="P19" s="14"/>
+    <row r="19" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A19" s="11"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="13"/>
+      <c r="K19" s="13"/>
+      <c r="L19" s="13"/>
+      <c r="M19" s="15"/>
+      <c r="N19" s="15"/>
+      <c r="O19" s="15"/>
+      <c r="P19" s="15"/>
       <c r="Q19" s="28"/>
       <c r="R19" s="28"/>
       <c r="S19" s="28"/>
-      <c r="T19" s="14"/>
+      <c r="T19" s="15"/>
       <c r="U19" s="28"/>
-      <c r="V19" s="13">
-        <v>0</v>
-      </c>
+      <c r="V19" s="13"/>
       <c r="W19" s="28"/>
-    </row>
-    <row r="20" spans="1:23" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="11">
-        <v>1003483344</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C20" s="4">
-        <v>875452.5</v>
-      </c>
-      <c r="D20" s="5">
-        <v>124547.49999999999</v>
-      </c>
-      <c r="E20" s="13">
-        <v>314406</v>
-      </c>
-      <c r="F20" s="13">
-        <v>140072.4</v>
-      </c>
-      <c r="G20" s="13">
-        <v>0</v>
-      </c>
-      <c r="H20" s="21">
-        <v>56000</v>
-      </c>
-      <c r="I20" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="J20" s="25">
-        <v>1118333.6000000001</v>
-      </c>
-      <c r="K20" s="13">
-        <v>0</v>
-      </c>
-      <c r="L20" s="13">
-        <v>0</v>
-      </c>
-      <c r="M20" s="13">
-        <v>0</v>
-      </c>
-      <c r="N20" s="27"/>
-      <c r="O20" s="14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="P20" s="14"/>
-      <c r="Q20" s="28"/>
-      <c r="R20" s="28"/>
-      <c r="S20" s="28"/>
-      <c r="T20" s="14"/>
-      <c r="U20" s="28"/>
-      <c r="V20" s="13">
-        <v>0</v>
-      </c>
-      <c r="W20" s="28"/>
-    </row>
-    <row r="21" spans="1:23" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="11">
-        <v>1119210446</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C21" s="4">
-        <v>817089</v>
-      </c>
-      <c r="D21" s="5">
-        <v>116244.33333333333</v>
-      </c>
-      <c r="E21" s="13">
-        <v>171914</v>
-      </c>
-      <c r="F21" s="13">
-        <v>65367.12</v>
-      </c>
-      <c r="G21" s="13">
-        <v>0</v>
-      </c>
-      <c r="H21" s="21">
-        <v>7000</v>
-      </c>
-      <c r="I21" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="J21" s="25">
-        <v>1032880.2133333335</v>
-      </c>
-      <c r="K21" s="13">
-        <v>66666.666666666672</v>
-      </c>
-      <c r="L21" s="13">
-        <v>0</v>
-      </c>
-      <c r="M21" s="13">
-        <v>0</v>
-      </c>
-      <c r="N21" s="27" t="s">
-        <v>56</v>
-      </c>
-      <c r="O21" s="14">
-        <f t="shared" si="0"/>
-        <v>66666.666666666672</v>
-      </c>
-      <c r="P21" s="14"/>
-      <c r="Q21" s="28"/>
-      <c r="R21" s="28"/>
-      <c r="S21" s="28"/>
-      <c r="T21" s="14"/>
-      <c r="U21" s="28"/>
-      <c r="V21" s="13">
-        <v>0</v>
-      </c>
-      <c r="W21" s="28"/>
-    </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A22" s="11"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="13"/>
-      <c r="K22" s="13"/>
-      <c r="L22" s="13"/>
-      <c r="M22" s="15"/>
-      <c r="N22" s="15"/>
-      <c r="O22" s="15"/>
-      <c r="P22" s="15"/>
-      <c r="Q22" s="28"/>
-      <c r="R22" s="28"/>
-      <c r="S22" s="28"/>
-      <c r="T22" s="15"/>
-      <c r="U22" s="28"/>
-      <c r="V22" s="13"/>
-      <c r="W22" s="28"/>
+      <c r="X19" s="13"/>
+      <c r="Y19" s="13"/>
+      <c r="Z19" s="13"/>
+      <c r="AA19" s="13"/>
+      <c r="AB19" s="13"/>
+      <c r="AC19" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/empleados.xlsx
+++ b/empleados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\NOMINA Y RRHH\NOMINA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C53A8D10-9D39-4D46-8A5A-939E63F8D274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{006309C9-E99C-4CAA-9656-3C882872B816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DA975529-9E83-4FFA-BD35-5CA808A15280}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
   <si>
     <t>CEDULA</t>
   </si>
@@ -197,9 +197,6 @@
     <t>RENTABILIDAD</t>
   </si>
   <si>
-    <t>CARTERA</t>
-  </si>
-  <si>
     <t>PORCENTAJE VENTAS</t>
   </si>
   <si>
@@ -228,6 +225,12 @@
   </si>
   <si>
     <t>COMISION VENTAS</t>
+  </si>
+  <si>
+    <t>CARTERA VENCIDA</t>
+  </si>
+  <si>
+    <t>0.14</t>
   </si>
 </sst>
 </file>
@@ -401,9 +404,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -453,6 +453,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -794,21 +797,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E263F044-EB2C-4A38-BF1B-A61CE6B829F6}">
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:AB32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.140625" style="16" customWidth="1"/>
-    <col min="2" max="2" width="39.28515625" style="17" customWidth="1"/>
-    <col min="3" max="3" width="12.85546875" style="18" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.28515625" style="18" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.85546875" style="18" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.7109375" style="18" customWidth="1"/>
-    <col min="7" max="7" width="13.28515625" style="18" customWidth="1"/>
-    <col min="8" max="8" width="13.85546875" style="18" customWidth="1"/>
-    <col min="9" max="9" width="61.140625" style="19" customWidth="1"/>
-    <col min="10" max="10" width="15" style="18" customWidth="1"/>
-    <col min="11" max="11" width="19.85546875" style="18" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.140625" style="18" customWidth="1"/>
+    <col min="1" max="1" width="14.140625" style="15" customWidth="1"/>
+    <col min="2" max="2" width="39.28515625" style="16" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" style="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.28515625" style="17" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.85546875" style="17" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.7109375" style="17" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" style="17" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" style="17" customWidth="1"/>
+    <col min="9" max="9" width="61.140625" style="18" customWidth="1"/>
+    <col min="10" max="10" width="15" style="17" customWidth="1"/>
+    <col min="11" max="11" width="19.85546875" style="17" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.140625" style="17" customWidth="1"/>
     <col min="13" max="13" width="15.28515625" style="10" customWidth="1"/>
     <col min="14" max="14" width="44.5703125" style="10" customWidth="1"/>
     <col min="15" max="16" width="15.85546875" style="10" customWidth="1"/>
@@ -817,17 +820,17 @@
     <col min="19" max="19" width="22.5703125" style="10" customWidth="1"/>
     <col min="20" max="20" width="15.85546875" style="10" customWidth="1"/>
     <col min="21" max="21" width="18.7109375" style="10" customWidth="1"/>
-    <col min="22" max="22" width="15.85546875" style="18" customWidth="1"/>
-    <col min="23" max="24" width="16.7109375" style="10" customWidth="1"/>
+    <col min="22" max="22" width="16.7109375" style="10" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="10" customWidth="1"/>
+    <col min="24" max="24" width="17.28515625" style="10" customWidth="1"/>
     <col min="25" max="25" width="14.42578125" style="10" customWidth="1"/>
-    <col min="26" max="26" width="17.28515625" style="10" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="10" customWidth="1"/>
-    <col min="28" max="28" width="15.7109375" style="10" customWidth="1"/>
-    <col min="29" max="29" width="16.140625" style="10" customWidth="1"/>
-    <col min="30" max="16384" width="11.42578125" style="10"/>
+    <col min="26" max="26" width="15.7109375" style="10" customWidth="1"/>
+    <col min="27" max="27" width="15.85546875" style="17" customWidth="1"/>
+    <col min="28" max="28" width="16.7109375" style="10" customWidth="1"/>
+    <col min="29" max="16384" width="11.42578125" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="27" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" ht="27" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -877,28 +880,28 @@
         <v>51</v>
       </c>
       <c r="Q1" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="R1" s="9" t="s">
         <v>52</v>
       </c>
       <c r="S1" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="T1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="T1" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="U1" s="9" t="s">
-        <v>56</v>
-      </c>
       <c r="V1" s="8" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="W1" s="8" t="s">
         <v>58</v>
       </c>
       <c r="X1" s="8" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="Y1" s="8" t="s">
         <v>59</v>
@@ -907,20 +910,17 @@
         <v>61</v>
       </c>
       <c r="AA1" s="8" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="AB1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="AC1" s="8" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="11">
+    <row r="2" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="28">
         <v>52114146</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="11" t="s">
         <v>13</v>
       </c>
       <c r="C2" s="1">
@@ -929,60 +929,83 @@
       <c r="D2" s="2">
         <v>0</v>
       </c>
-      <c r="E2" s="13">
-        <v>0</v>
-      </c>
-      <c r="F2" s="13">
+      <c r="E2" s="12">
+        <v>0</v>
+      </c>
+      <c r="F2" s="12">
         <v>640000.00000000012</v>
       </c>
-      <c r="G2" s="13">
-        <v>0</v>
-      </c>
-      <c r="H2" s="21">
+      <c r="G2" s="12">
+        <v>0</v>
+      </c>
+      <c r="H2" s="20">
         <v>360000</v>
       </c>
-      <c r="I2" s="22" t="s">
+      <c r="I2" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="J2" s="24">
+      <c r="J2" s="23">
         <v>3000000.0000000005</v>
       </c>
-      <c r="K2" s="13">
-        <v>0</v>
-      </c>
-      <c r="L2" s="13">
-        <v>0</v>
-      </c>
-      <c r="M2" s="13">
-        <v>0</v>
-      </c>
-      <c r="N2" s="20"/>
-      <c r="O2" s="14">
+      <c r="K2" s="12">
+        <v>0</v>
+      </c>
+      <c r="L2" s="12">
+        <v>0</v>
+      </c>
+      <c r="M2" s="12">
+        <v>0</v>
+      </c>
+      <c r="N2" s="19"/>
+      <c r="O2" s="13">
         <f>K2-L2-M2</f>
         <v>0</v>
       </c>
-      <c r="P2" s="14"/>
-      <c r="Q2" s="28"/>
-      <c r="R2" s="28"/>
-      <c r="S2" s="28"/>
-      <c r="T2" s="14"/>
-      <c r="U2" s="28"/>
-      <c r="V2" s="13">
-        <v>0</v>
-      </c>
-      <c r="W2" s="28"/>
-      <c r="X2" s="13"/>
-      <c r="Y2" s="13"/>
-      <c r="Z2" s="13"/>
-      <c r="AA2" s="13"/>
-      <c r="AB2" s="13"/>
-      <c r="AC2" s="13"/>
-    </row>
-    <row r="3" spans="1:29" ht="27" x14ac:dyDescent="0.25">
-      <c r="A3" s="11">
+      <c r="P2" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="27">
+        <v>0</v>
+      </c>
+      <c r="R2" s="27">
+        <v>0</v>
+      </c>
+      <c r="S2" s="27">
+        <v>0</v>
+      </c>
+      <c r="T2" s="13">
+        <v>0</v>
+      </c>
+      <c r="U2" s="27">
+        <v>0</v>
+      </c>
+      <c r="V2" s="12">
+        <v>0</v>
+      </c>
+      <c r="W2" s="12">
+        <v>0</v>
+      </c>
+      <c r="X2" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" ht="27" x14ac:dyDescent="0.25">
+      <c r="A3" s="28">
         <v>94288721</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="11" t="s">
         <v>14</v>
       </c>
       <c r="C3" s="4">
@@ -991,62 +1014,85 @@
       <c r="D3" s="5">
         <v>124547.49999999999</v>
       </c>
-      <c r="E3" s="13">
-        <v>0</v>
-      </c>
-      <c r="F3" s="13">
+      <c r="E3" s="12">
+        <v>0</v>
+      </c>
+      <c r="F3" s="12">
         <v>140072.4</v>
       </c>
-      <c r="G3" s="13">
+      <c r="G3" s="12">
         <v>700000</v>
       </c>
-      <c r="H3" s="21">
+      <c r="H3" s="20">
         <v>29871</v>
       </c>
-      <c r="I3" s="22" t="s">
+      <c r="I3" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="25">
+      <c r="J3" s="24">
         <v>1530056.6</v>
       </c>
-      <c r="K3" s="13">
+      <c r="K3" s="12">
         <v>634511</v>
       </c>
-      <c r="L3" s="13">
+      <c r="L3" s="12">
         <v>56000</v>
       </c>
-      <c r="M3" s="13">
+      <c r="M3" s="12">
         <v>578511</v>
       </c>
-      <c r="N3" s="20" t="s">
+      <c r="N3" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="O3" s="14">
+      <c r="O3" s="13">
         <f t="shared" ref="O3:O18" si="0">K3-L3-M3</f>
         <v>0</v>
       </c>
-      <c r="P3" s="14"/>
-      <c r="Q3" s="28"/>
-      <c r="R3" s="28"/>
-      <c r="S3" s="28"/>
-      <c r="T3" s="14"/>
-      <c r="U3" s="28"/>
-      <c r="V3" s="13">
-        <v>0</v>
-      </c>
-      <c r="W3" s="28"/>
-      <c r="X3" s="13"/>
-      <c r="Y3" s="13"/>
-      <c r="Z3" s="13"/>
-      <c r="AA3" s="13"/>
-      <c r="AB3" s="13"/>
-      <c r="AC3" s="13"/>
-    </row>
-    <row r="4" spans="1:29" ht="27" x14ac:dyDescent="0.25">
-      <c r="A4" s="11">
+      <c r="P3" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="27">
+        <v>0</v>
+      </c>
+      <c r="R3" s="27">
+        <v>0</v>
+      </c>
+      <c r="S3" s="27">
+        <v>0</v>
+      </c>
+      <c r="T3" s="13">
+        <v>0</v>
+      </c>
+      <c r="U3" s="27">
+        <v>0</v>
+      </c>
+      <c r="V3" s="12">
+        <v>0</v>
+      </c>
+      <c r="W3" s="12">
+        <v>0</v>
+      </c>
+      <c r="X3" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" ht="27" x14ac:dyDescent="0.25">
+      <c r="A4" s="28">
         <v>1001200622</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="11" t="s">
         <v>15</v>
       </c>
       <c r="C4" s="4">
@@ -1055,58 +1101,81 @@
       <c r="D4" s="5">
         <v>124547.49999999999</v>
       </c>
-      <c r="E4" s="13">
-        <v>0</v>
-      </c>
-      <c r="F4" s="13">
+      <c r="E4" s="12">
+        <v>0</v>
+      </c>
+      <c r="F4" s="12">
         <v>140072.4</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="12">
         <v>600000</v>
       </c>
-      <c r="H4" s="21"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="25">
+      <c r="H4" s="20"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="24">
         <v>1459927.6</v>
       </c>
-      <c r="K4" s="13">
+      <c r="K4" s="12">
         <v>650000</v>
       </c>
-      <c r="L4" s="13">
+      <c r="L4" s="12">
         <v>56000</v>
       </c>
-      <c r="M4" s="13">
+      <c r="M4" s="12">
         <v>594000</v>
       </c>
-      <c r="N4" s="26" t="s">
+      <c r="N4" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="O4" s="14">
+      <c r="O4" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P4" s="14"/>
-      <c r="Q4" s="28"/>
-      <c r="R4" s="28"/>
-      <c r="S4" s="28"/>
-      <c r="T4" s="14"/>
-      <c r="U4" s="28"/>
-      <c r="V4" s="13">
-        <v>0</v>
-      </c>
-      <c r="W4" s="28"/>
-      <c r="X4" s="13"/>
-      <c r="Y4" s="13"/>
-      <c r="Z4" s="13"/>
-      <c r="AA4" s="13"/>
-      <c r="AB4" s="13"/>
-      <c r="AC4" s="13"/>
-    </row>
-    <row r="5" spans="1:29" ht="27" x14ac:dyDescent="0.25">
-      <c r="A5" s="11">
+      <c r="P4" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="27">
+        <v>0</v>
+      </c>
+      <c r="R4" s="27">
+        <v>0</v>
+      </c>
+      <c r="S4" s="27">
+        <v>0</v>
+      </c>
+      <c r="T4" s="13">
+        <v>0</v>
+      </c>
+      <c r="U4" s="27">
+        <v>0</v>
+      </c>
+      <c r="V4" s="12">
+        <v>0</v>
+      </c>
+      <c r="W4" s="12">
+        <v>0</v>
+      </c>
+      <c r="X4" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" ht="27" x14ac:dyDescent="0.25">
+      <c r="A5" s="28">
         <v>1001045472</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="11" t="s">
         <v>16</v>
       </c>
       <c r="C5" s="4">
@@ -1115,72 +1184,81 @@
       <c r="D5" s="5">
         <v>124547.49999999999</v>
       </c>
-      <c r="E5" s="13">
-        <v>0</v>
-      </c>
-      <c r="F5" s="13">
+      <c r="E5" s="12">
+        <v>0</v>
+      </c>
+      <c r="F5" s="12">
         <v>140072.4</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="12">
         <v>700000</v>
       </c>
-      <c r="H5" s="21"/>
-      <c r="I5" s="22"/>
-      <c r="J5" s="25">
+      <c r="H5" s="20"/>
+      <c r="I5" s="21"/>
+      <c r="J5" s="24">
         <v>1559927.6</v>
       </c>
-      <c r="K5" s="13">
+      <c r="K5" s="12">
         <v>777558</v>
       </c>
-      <c r="L5" s="13">
+      <c r="L5" s="12">
         <v>186726</v>
       </c>
-      <c r="M5" s="13">
+      <c r="M5" s="12">
         <v>242000</v>
       </c>
-      <c r="N5" s="20" t="s">
+      <c r="N5" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="O5" s="14">
+      <c r="O5" s="13">
         <f t="shared" si="0"/>
         <v>348832</v>
       </c>
-      <c r="P5" s="14">
+      <c r="P5" s="13">
         <v>123456789</v>
       </c>
-      <c r="Q5" s="28"/>
-      <c r="R5" s="28"/>
-      <c r="S5" s="28"/>
-      <c r="T5" s="14"/>
-      <c r="U5" s="28"/>
-      <c r="V5" s="13">
-        <v>0</v>
-      </c>
-      <c r="W5" s="28"/>
-      <c r="X5" s="13">
+      <c r="Q5" s="27">
+        <v>0</v>
+      </c>
+      <c r="R5" s="27">
+        <v>0</v>
+      </c>
+      <c r="S5" s="27">
+        <v>0</v>
+      </c>
+      <c r="T5" s="13">
+        <v>0</v>
+      </c>
+      <c r="U5" s="27">
+        <v>0</v>
+      </c>
+      <c r="V5" s="12">
         <v>1500000</v>
       </c>
-      <c r="Y5" s="13">
+      <c r="W5" s="12">
         <v>123456789</v>
       </c>
-      <c r="Z5" s="13">
+      <c r="X5" s="12">
         <v>1500000</v>
       </c>
-      <c r="AA5" s="13">
+      <c r="Y5" s="12">
         <v>123456789</v>
       </c>
-      <c r="AB5" s="13">
+      <c r="Z5" s="12">
         <v>1500000</v>
       </c>
-      <c r="AC5" s="13">
+      <c r="AA5" s="12">
         <v>3000000</v>
       </c>
-    </row>
-    <row r="6" spans="1:29" ht="27" x14ac:dyDescent="0.25">
-      <c r="A6" s="11">
+      <c r="AB5" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" ht="27" x14ac:dyDescent="0.25">
+      <c r="A6" s="28">
         <v>80875830</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="11" t="s">
         <v>17</v>
       </c>
       <c r="C6" s="4">
@@ -1189,60 +1267,83 @@
       <c r="D6" s="5">
         <v>49819</v>
       </c>
-      <c r="E6" s="13">
-        <v>0</v>
-      </c>
-      <c r="F6" s="13">
+      <c r="E6" s="12">
+        <v>0</v>
+      </c>
+      <c r="F6" s="12">
         <v>135403.32</v>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="12">
         <v>700000</v>
       </c>
-      <c r="H6" s="21"/>
-      <c r="I6" s="22" t="s">
+      <c r="H6" s="20"/>
+      <c r="I6" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="J6" s="25">
+      <c r="J6" s="24">
         <v>1489868.18</v>
       </c>
-      <c r="K6" s="13">
+      <c r="K6" s="12">
         <v>1589070</v>
       </c>
-      <c r="L6" s="13">
+      <c r="L6" s="12">
         <v>35000</v>
       </c>
-      <c r="M6" s="13">
+      <c r="M6" s="12">
         <v>612901</v>
       </c>
-      <c r="N6" s="20" t="s">
+      <c r="N6" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="O6" s="14">
+      <c r="O6" s="13">
         <f t="shared" si="0"/>
         <v>941169</v>
       </c>
-      <c r="P6" s="14"/>
-      <c r="Q6" s="28"/>
-      <c r="R6" s="28"/>
-      <c r="S6" s="28"/>
-      <c r="T6" s="14"/>
-      <c r="U6" s="28"/>
-      <c r="V6" s="13">
-        <v>0</v>
-      </c>
-      <c r="W6" s="28"/>
-      <c r="X6" s="13"/>
-      <c r="Y6" s="13"/>
-      <c r="Z6" s="13"/>
-      <c r="AA6" s="13"/>
-      <c r="AB6" s="13"/>
-      <c r="AC6" s="13"/>
-    </row>
-    <row r="7" spans="1:29" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="11">
+      <c r="P6" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="27">
+        <v>0</v>
+      </c>
+      <c r="R6" s="27">
+        <v>0</v>
+      </c>
+      <c r="S6" s="27">
+        <v>0</v>
+      </c>
+      <c r="T6" s="13">
+        <v>0</v>
+      </c>
+      <c r="U6" s="27">
+        <v>0</v>
+      </c>
+      <c r="V6" s="12">
+        <v>0</v>
+      </c>
+      <c r="W6" s="12">
+        <v>0</v>
+      </c>
+      <c r="X6" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="28">
         <v>1006116706</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="11" t="s">
         <v>18</v>
       </c>
       <c r="C7" s="4">
@@ -1251,60 +1352,83 @@
       <c r="D7" s="5">
         <v>58122.166666666664</v>
       </c>
-      <c r="E7" s="13">
-        <v>0</v>
-      </c>
-      <c r="F7" s="13">
+      <c r="E7" s="12">
+        <v>0</v>
+      </c>
+      <c r="F7" s="12">
         <v>140072.4</v>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="12">
         <v>100000</v>
       </c>
-      <c r="H7" s="21">
+      <c r="H7" s="20">
         <v>250000</v>
       </c>
-      <c r="I7" s="22" t="s">
+      <c r="I7" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="J7" s="25">
+      <c r="J7" s="24">
         <v>643502.2666666666</v>
       </c>
-      <c r="K7" s="13">
-        <v>0</v>
-      </c>
-      <c r="L7" s="13">
-        <v>0</v>
-      </c>
-      <c r="M7" s="13">
-        <v>0</v>
-      </c>
-      <c r="N7" s="27"/>
-      <c r="O7" s="14">
+      <c r="K7" s="12">
+        <v>0</v>
+      </c>
+      <c r="L7" s="12">
+        <v>0</v>
+      </c>
+      <c r="M7" s="12">
+        <v>0</v>
+      </c>
+      <c r="N7" s="26"/>
+      <c r="O7" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P7" s="14"/>
-      <c r="Q7" s="28"/>
-      <c r="R7" s="28"/>
-      <c r="S7" s="28"/>
-      <c r="T7" s="14"/>
-      <c r="U7" s="28"/>
-      <c r="V7" s="13">
-        <v>0</v>
-      </c>
-      <c r="W7" s="28"/>
-      <c r="X7" s="13"/>
-      <c r="Y7" s="13"/>
-      <c r="Z7" s="13"/>
-      <c r="AA7" s="13"/>
-      <c r="AB7" s="13"/>
-      <c r="AC7" s="13"/>
-    </row>
-    <row r="8" spans="1:29" ht="27" x14ac:dyDescent="0.25">
-      <c r="A8" s="11">
+      <c r="P7" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="27">
+        <v>0</v>
+      </c>
+      <c r="R7" s="27">
+        <v>0</v>
+      </c>
+      <c r="S7" s="27">
+        <v>0</v>
+      </c>
+      <c r="T7" s="13">
+        <v>0</v>
+      </c>
+      <c r="U7" s="27">
+        <v>0</v>
+      </c>
+      <c r="V7" s="12">
+        <v>0</v>
+      </c>
+      <c r="W7" s="12">
+        <v>0</v>
+      </c>
+      <c r="X7" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" ht="27" x14ac:dyDescent="0.25">
+      <c r="A8" s="28">
         <v>1193092448</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="11" t="s">
         <v>19</v>
       </c>
       <c r="C8" s="4">
@@ -1313,58 +1437,81 @@
       <c r="D8" s="5">
         <v>124547.49999999999</v>
       </c>
-      <c r="E8" s="13">
-        <v>0</v>
-      </c>
-      <c r="F8" s="13">
+      <c r="E8" s="12">
+        <v>0</v>
+      </c>
+      <c r="F8" s="12">
         <v>140072.4</v>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="12">
         <v>700000</v>
       </c>
-      <c r="H8" s="21"/>
-      <c r="I8" s="22"/>
-      <c r="J8" s="25">
+      <c r="H8" s="20"/>
+      <c r="I8" s="21"/>
+      <c r="J8" s="24">
         <v>1559927.6</v>
       </c>
-      <c r="K8" s="13">
+      <c r="K8" s="12">
         <v>550000</v>
       </c>
-      <c r="L8" s="13">
+      <c r="L8" s="12">
         <v>144726</v>
       </c>
-      <c r="M8" s="13">
+      <c r="M8" s="12">
         <v>336331</v>
       </c>
-      <c r="N8" s="26" t="s">
+      <c r="N8" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="O8" s="14">
+      <c r="O8" s="13">
         <f t="shared" si="0"/>
         <v>68943</v>
       </c>
-      <c r="P8" s="14"/>
-      <c r="Q8" s="28"/>
-      <c r="R8" s="28"/>
-      <c r="S8" s="28"/>
-      <c r="T8" s="14"/>
-      <c r="U8" s="28"/>
-      <c r="V8" s="13">
-        <v>0</v>
-      </c>
-      <c r="W8" s="28"/>
-      <c r="X8" s="13"/>
-      <c r="Y8" s="13"/>
-      <c r="Z8" s="13"/>
-      <c r="AA8" s="13"/>
-      <c r="AB8" s="13"/>
-      <c r="AC8" s="13"/>
-    </row>
-    <row r="9" spans="1:29" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="11">
+      <c r="P8" s="13">
+        <v>90000000</v>
+      </c>
+      <c r="Q8" s="27">
+        <v>30</v>
+      </c>
+      <c r="R8" s="27">
+        <v>35</v>
+      </c>
+      <c r="S8" s="27">
+        <v>100</v>
+      </c>
+      <c r="T8" s="13">
+        <v>2000000</v>
+      </c>
+      <c r="U8" s="27">
+        <v>20</v>
+      </c>
+      <c r="V8" s="12">
+        <v>0</v>
+      </c>
+      <c r="W8" s="12">
+        <v>0</v>
+      </c>
+      <c r="X8" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="12">
+        <v>3000000</v>
+      </c>
+      <c r="AB8" s="27">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="28">
         <v>79910037</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="11" t="s">
         <v>20</v>
       </c>
       <c r="C9" s="4">
@@ -1373,60 +1520,83 @@
       <c r="D9" s="5">
         <v>124547.49999999999</v>
       </c>
-      <c r="E9" s="13">
-        <v>0</v>
-      </c>
-      <c r="F9" s="13">
+      <c r="E9" s="12">
+        <v>0</v>
+      </c>
+      <c r="F9" s="12">
         <v>140072.4</v>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="12">
         <v>300000</v>
       </c>
-      <c r="H9" s="21">
+      <c r="H9" s="20">
         <v>353000</v>
       </c>
-      <c r="I9" s="22" t="s">
+      <c r="I9" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="J9" s="25">
+      <c r="J9" s="24">
         <v>806927.6</v>
       </c>
-      <c r="K9" s="13">
+      <c r="K9" s="12">
         <v>-300000</v>
       </c>
-      <c r="L9" s="13">
-        <v>0</v>
-      </c>
-      <c r="M9" s="13">
-        <v>0</v>
-      </c>
-      <c r="N9" s="20"/>
-      <c r="O9" s="14">
+      <c r="L9" s="12">
+        <v>0</v>
+      </c>
+      <c r="M9" s="12">
+        <v>0</v>
+      </c>
+      <c r="N9" s="19"/>
+      <c r="O9" s="13">
         <f t="shared" si="0"/>
         <v>-300000</v>
       </c>
-      <c r="P9" s="14"/>
-      <c r="Q9" s="28"/>
-      <c r="R9" s="28"/>
-      <c r="S9" s="28"/>
-      <c r="T9" s="14"/>
-      <c r="U9" s="28"/>
-      <c r="V9" s="13">
-        <v>0</v>
-      </c>
-      <c r="W9" s="28"/>
-      <c r="X9" s="13"/>
-      <c r="Y9" s="13"/>
-      <c r="Z9" s="13"/>
-      <c r="AA9" s="13"/>
-      <c r="AB9" s="13"/>
-      <c r="AC9" s="13"/>
-    </row>
-    <row r="10" spans="1:29" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="11">
+      <c r="P9" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="27">
+        <v>0</v>
+      </c>
+      <c r="R9" s="27">
+        <v>0</v>
+      </c>
+      <c r="S9" s="27">
+        <v>0</v>
+      </c>
+      <c r="T9" s="13">
+        <v>0</v>
+      </c>
+      <c r="U9" s="27">
+        <v>0</v>
+      </c>
+      <c r="V9" s="12">
+        <v>0</v>
+      </c>
+      <c r="W9" s="12">
+        <v>0</v>
+      </c>
+      <c r="X9" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="28">
         <v>1000795016</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="11" t="s">
         <v>21</v>
       </c>
       <c r="C10" s="4">
@@ -1435,56 +1605,79 @@
       <c r="D10" s="5">
         <v>124547.49999999999</v>
       </c>
-      <c r="E10" s="13">
-        <v>0</v>
-      </c>
-      <c r="F10" s="13">
+      <c r="E10" s="12">
+        <v>0</v>
+      </c>
+      <c r="F10" s="12">
         <v>172000</v>
       </c>
-      <c r="G10" s="13">
+      <c r="G10" s="12">
         <v>850000</v>
       </c>
-      <c r="H10" s="21"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="25">
+      <c r="H10" s="20"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="24">
         <v>1877547.5</v>
       </c>
-      <c r="K10" s="13">
-        <v>0</v>
-      </c>
-      <c r="L10" s="13">
-        <v>0</v>
-      </c>
-      <c r="M10" s="13">
-        <v>0</v>
-      </c>
-      <c r="N10" s="27"/>
-      <c r="O10" s="14">
+      <c r="K10" s="12">
+        <v>0</v>
+      </c>
+      <c r="L10" s="12">
+        <v>0</v>
+      </c>
+      <c r="M10" s="12">
+        <v>0</v>
+      </c>
+      <c r="N10" s="26"/>
+      <c r="O10" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P10" s="14"/>
-      <c r="Q10" s="28"/>
-      <c r="R10" s="28"/>
-      <c r="S10" s="28"/>
-      <c r="T10" s="14"/>
-      <c r="U10" s="28"/>
-      <c r="V10" s="13">
-        <v>0</v>
-      </c>
-      <c r="W10" s="28"/>
-      <c r="X10" s="13"/>
-      <c r="Y10" s="13"/>
-      <c r="Z10" s="13"/>
-      <c r="AA10" s="13"/>
-      <c r="AB10" s="13"/>
-      <c r="AC10" s="13"/>
-    </row>
-    <row r="11" spans="1:29" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="11">
+      <c r="P10" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="27">
+        <v>0</v>
+      </c>
+      <c r="R10" s="27">
+        <v>0</v>
+      </c>
+      <c r="S10" s="27">
+        <v>0</v>
+      </c>
+      <c r="T10" s="13">
+        <v>0</v>
+      </c>
+      <c r="U10" s="27">
+        <v>0</v>
+      </c>
+      <c r="V10" s="12">
+        <v>0</v>
+      </c>
+      <c r="W10" s="12">
+        <v>0</v>
+      </c>
+      <c r="X10" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="28">
         <v>79593400</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="11" t="s">
         <v>22</v>
       </c>
       <c r="C11" s="4">
@@ -1493,56 +1686,79 @@
       <c r="D11" s="5">
         <v>0</v>
       </c>
-      <c r="E11" s="13">
-        <v>0</v>
-      </c>
-      <c r="F11" s="13">
+      <c r="E11" s="12">
+        <v>0</v>
+      </c>
+      <c r="F11" s="12">
         <v>572000</v>
       </c>
-      <c r="G11" s="13">
+      <c r="G11" s="12">
         <v>2000000</v>
       </c>
-      <c r="H11" s="21"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="25">
+      <c r="H11" s="20"/>
+      <c r="I11" s="21"/>
+      <c r="J11" s="24">
         <v>8578000</v>
       </c>
-      <c r="K11" s="13">
+      <c r="K11" s="12">
         <v>572000</v>
       </c>
-      <c r="L11" s="13">
-        <v>0</v>
-      </c>
-      <c r="M11" s="13">
-        <v>0</v>
-      </c>
-      <c r="N11" s="27"/>
-      <c r="O11" s="14">
+      <c r="L11" s="12">
+        <v>0</v>
+      </c>
+      <c r="M11" s="12">
+        <v>0</v>
+      </c>
+      <c r="N11" s="26"/>
+      <c r="O11" s="13">
         <f t="shared" si="0"/>
         <v>572000</v>
       </c>
-      <c r="P11" s="14"/>
-      <c r="Q11" s="28"/>
-      <c r="R11" s="28"/>
-      <c r="S11" s="28"/>
-      <c r="T11" s="14"/>
-      <c r="U11" s="28"/>
-      <c r="V11" s="13">
-        <v>0</v>
-      </c>
-      <c r="W11" s="28"/>
-      <c r="X11" s="13"/>
-      <c r="Y11" s="13"/>
-      <c r="Z11" s="13"/>
-      <c r="AA11" s="13"/>
-      <c r="AB11" s="13"/>
-      <c r="AC11" s="13"/>
-    </row>
-    <row r="12" spans="1:29" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="11">
+      <c r="P11" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="27">
+        <v>0</v>
+      </c>
+      <c r="R11" s="27">
+        <v>0</v>
+      </c>
+      <c r="S11" s="27">
+        <v>0</v>
+      </c>
+      <c r="T11" s="13">
+        <v>0</v>
+      </c>
+      <c r="U11" s="27">
+        <v>0</v>
+      </c>
+      <c r="V11" s="12">
+        <v>0</v>
+      </c>
+      <c r="W11" s="12">
+        <v>0</v>
+      </c>
+      <c r="X11" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="28">
         <v>1023029896</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C12" s="4">
@@ -1551,60 +1767,83 @@
       <c r="D12" s="5">
         <v>124547.49999999999</v>
       </c>
-      <c r="E12" s="13">
-        <v>0</v>
-      </c>
-      <c r="F12" s="13">
+      <c r="E12" s="12">
+        <v>0</v>
+      </c>
+      <c r="F12" s="12">
         <v>140072.4</v>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="12">
         <v>100000</v>
       </c>
-      <c r="H12" s="21">
+      <c r="H12" s="20">
         <v>7000</v>
       </c>
-      <c r="I12" s="22" t="s">
+      <c r="I12" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="J12" s="25">
+      <c r="J12" s="24">
         <v>952927.6</v>
       </c>
-      <c r="K12" s="13">
-        <v>0</v>
-      </c>
-      <c r="L12" s="13">
-        <v>0</v>
-      </c>
-      <c r="M12" s="13">
-        <v>0</v>
-      </c>
-      <c r="N12" s="27"/>
-      <c r="O12" s="14">
+      <c r="K12" s="12">
+        <v>0</v>
+      </c>
+      <c r="L12" s="12">
+        <v>0</v>
+      </c>
+      <c r="M12" s="12">
+        <v>0</v>
+      </c>
+      <c r="N12" s="26"/>
+      <c r="O12" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P12" s="14"/>
-      <c r="Q12" s="28"/>
-      <c r="R12" s="28"/>
-      <c r="S12" s="28"/>
-      <c r="T12" s="14"/>
-      <c r="U12" s="28"/>
-      <c r="V12" s="13">
-        <v>0</v>
-      </c>
-      <c r="W12" s="28"/>
-      <c r="X12" s="13"/>
-      <c r="Y12" s="13"/>
-      <c r="Z12" s="13"/>
-      <c r="AA12" s="13"/>
-      <c r="AB12" s="13"/>
-      <c r="AC12" s="13"/>
-    </row>
-    <row r="13" spans="1:29" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="11">
+      <c r="P12" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="27">
+        <v>0</v>
+      </c>
+      <c r="R12" s="27">
+        <v>0</v>
+      </c>
+      <c r="S12" s="27">
+        <v>0</v>
+      </c>
+      <c r="T12" s="13">
+        <v>0</v>
+      </c>
+      <c r="U12" s="27">
+        <v>0</v>
+      </c>
+      <c r="V12" s="12">
+        <v>0</v>
+      </c>
+      <c r="W12" s="12">
+        <v>0</v>
+      </c>
+      <c r="X12" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="28">
         <v>1015473856</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C13" s="4">
@@ -1613,60 +1852,83 @@
       <c r="D13" s="5">
         <v>99638</v>
       </c>
-      <c r="E13" s="13">
-        <v>0</v>
-      </c>
-      <c r="F13" s="13">
+      <c r="E13" s="12">
+        <v>0</v>
+      </c>
+      <c r="F13" s="12">
         <v>146666.66666666666</v>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="12">
         <v>600000</v>
       </c>
-      <c r="H13" s="21"/>
-      <c r="I13" s="22" t="s">
+      <c r="H13" s="20"/>
+      <c r="I13" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="J13" s="25">
+      <c r="J13" s="24">
         <v>1652971.3333333333</v>
       </c>
-      <c r="K13" s="13">
-        <v>0</v>
-      </c>
-      <c r="L13" s="13">
-        <v>0</v>
-      </c>
-      <c r="M13" s="13">
-        <v>0</v>
-      </c>
-      <c r="N13" s="27" t="s">
+      <c r="K13" s="12">
+        <v>0</v>
+      </c>
+      <c r="L13" s="12">
+        <v>0</v>
+      </c>
+      <c r="M13" s="12">
+        <v>0</v>
+      </c>
+      <c r="N13" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="O13" s="14">
+      <c r="O13" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P13" s="14"/>
-      <c r="Q13" s="28"/>
-      <c r="R13" s="28"/>
-      <c r="S13" s="28"/>
-      <c r="T13" s="14"/>
-      <c r="U13" s="28"/>
-      <c r="V13" s="13">
-        <v>0</v>
-      </c>
-      <c r="W13" s="28"/>
-      <c r="X13" s="13"/>
-      <c r="Y13" s="13"/>
-      <c r="Z13" s="13"/>
-      <c r="AA13" s="13"/>
-      <c r="AB13" s="13"/>
-      <c r="AC13" s="13"/>
-    </row>
-    <row r="14" spans="1:29" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="11">
+      <c r="P13" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="27">
+        <v>0</v>
+      </c>
+      <c r="R13" s="27">
+        <v>0</v>
+      </c>
+      <c r="S13" s="27">
+        <v>0</v>
+      </c>
+      <c r="T13" s="13">
+        <v>0</v>
+      </c>
+      <c r="U13" s="27">
+        <v>0</v>
+      </c>
+      <c r="V13" s="12">
+        <v>0</v>
+      </c>
+      <c r="W13" s="12">
+        <v>0</v>
+      </c>
+      <c r="X13" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="28">
         <v>1003533086</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C14" s="4">
@@ -1675,60 +1937,83 @@
       <c r="D14" s="5">
         <v>124547.49999999999</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="12">
         <v>316367</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="12">
         <v>140072.4</v>
       </c>
-      <c r="G14" s="13">
-        <v>0</v>
-      </c>
-      <c r="H14" s="21">
+      <c r="G14" s="12">
+        <v>0</v>
+      </c>
+      <c r="H14" s="20">
         <v>245400</v>
       </c>
-      <c r="I14" s="22" t="s">
+      <c r="I14" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="J14" s="25">
+      <c r="J14" s="24">
         <v>930894.6</v>
       </c>
-      <c r="K14" s="13">
-        <v>0</v>
-      </c>
-      <c r="L14" s="13">
-        <v>0</v>
-      </c>
-      <c r="M14" s="13">
-        <v>0</v>
-      </c>
-      <c r="N14" s="27"/>
-      <c r="O14" s="14">
+      <c r="K14" s="12">
+        <v>0</v>
+      </c>
+      <c r="L14" s="12">
+        <v>0</v>
+      </c>
+      <c r="M14" s="12">
+        <v>0</v>
+      </c>
+      <c r="N14" s="26"/>
+      <c r="O14" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P14" s="14"/>
-      <c r="Q14" s="28"/>
-      <c r="R14" s="28"/>
-      <c r="S14" s="28"/>
-      <c r="T14" s="14"/>
-      <c r="U14" s="28"/>
-      <c r="V14" s="13">
-        <v>0</v>
-      </c>
-      <c r="W14" s="28"/>
-      <c r="X14" s="13"/>
-      <c r="Y14" s="13"/>
-      <c r="Z14" s="13"/>
-      <c r="AA14" s="13"/>
-      <c r="AB14" s="13"/>
-      <c r="AC14" s="13"/>
-    </row>
-    <row r="15" spans="1:29" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="11">
+      <c r="P14" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="27">
+        <v>0</v>
+      </c>
+      <c r="R14" s="27">
+        <v>0</v>
+      </c>
+      <c r="S14" s="27">
+        <v>0</v>
+      </c>
+      <c r="T14" s="13">
+        <v>0</v>
+      </c>
+      <c r="U14" s="27">
+        <v>0</v>
+      </c>
+      <c r="V14" s="12">
+        <v>0</v>
+      </c>
+      <c r="W14" s="12">
+        <v>0</v>
+      </c>
+      <c r="X14" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="28">
         <v>1028660836</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C15" s="4">
@@ -1737,62 +2022,85 @@
       <c r="D15" s="5">
         <v>124547.49999999999</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="12">
         <v>60861</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="12">
         <v>135403.32</v>
       </c>
-      <c r="G15" s="13">
-        <v>0</v>
-      </c>
-      <c r="H15" s="21">
+      <c r="G15" s="12">
+        <v>0</v>
+      </c>
+      <c r="H15" s="20">
         <v>233166</v>
       </c>
-      <c r="I15" s="22" t="s">
+      <c r="I15" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="J15" s="25">
+      <c r="J15" s="24">
         <v>692291.67999999993</v>
       </c>
-      <c r="K15" s="13">
+      <c r="K15" s="12">
         <v>335324</v>
       </c>
-      <c r="L15" s="13">
-        <v>0</v>
-      </c>
-      <c r="M15" s="13">
+      <c r="L15" s="12">
+        <v>0</v>
+      </c>
+      <c r="M15" s="12">
         <v>335324</v>
       </c>
-      <c r="N15" s="27" t="s">
+      <c r="N15" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="O15" s="14">
+      <c r="O15" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P15" s="14"/>
-      <c r="Q15" s="28"/>
-      <c r="R15" s="28"/>
-      <c r="S15" s="28"/>
-      <c r="T15" s="14"/>
-      <c r="U15" s="28"/>
-      <c r="V15" s="13">
-        <v>0</v>
-      </c>
-      <c r="W15" s="28"/>
-      <c r="X15" s="13"/>
-      <c r="Y15" s="13"/>
-      <c r="Z15" s="13"/>
-      <c r="AA15" s="13"/>
-      <c r="AB15" s="13"/>
-      <c r="AC15" s="13"/>
-    </row>
-    <row r="16" spans="1:29" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="11">
+      <c r="P15" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="27">
+        <v>0</v>
+      </c>
+      <c r="R15" s="27">
+        <v>0</v>
+      </c>
+      <c r="S15" s="27">
+        <v>0</v>
+      </c>
+      <c r="T15" s="13">
+        <v>0</v>
+      </c>
+      <c r="U15" s="27">
+        <v>0</v>
+      </c>
+      <c r="V15" s="12">
+        <v>0</v>
+      </c>
+      <c r="W15" s="12">
+        <v>0</v>
+      </c>
+      <c r="X15" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A16" s="28">
         <v>1053330769</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="11" t="s">
         <v>27</v>
       </c>
       <c r="C16" s="4">
@@ -1801,60 +2109,83 @@
       <c r="D16" s="5">
         <v>116244.33333333333</v>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="12">
         <v>280770</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="12">
         <v>135403.32</v>
       </c>
-      <c r="G16" s="13">
-        <v>0</v>
-      </c>
-      <c r="H16" s="21">
+      <c r="G16" s="12">
+        <v>0</v>
+      </c>
+      <c r="H16" s="20">
         <v>59000</v>
       </c>
-      <c r="I16" s="23" t="s">
+      <c r="I16" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="J16" s="25">
+      <c r="J16" s="24">
         <v>1078063.5133333334</v>
       </c>
-      <c r="K16" s="13">
-        <v>0</v>
-      </c>
-      <c r="L16" s="13">
-        <v>0</v>
-      </c>
-      <c r="M16" s="13">
-        <v>0</v>
-      </c>
-      <c r="N16" s="27"/>
-      <c r="O16" s="14">
+      <c r="K16" s="12">
+        <v>0</v>
+      </c>
+      <c r="L16" s="12">
+        <v>0</v>
+      </c>
+      <c r="M16" s="12">
+        <v>0</v>
+      </c>
+      <c r="N16" s="26"/>
+      <c r="O16" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P16" s="14"/>
-      <c r="Q16" s="28"/>
-      <c r="R16" s="28"/>
-      <c r="S16" s="28"/>
-      <c r="T16" s="14"/>
-      <c r="U16" s="28"/>
-      <c r="V16" s="13">
-        <v>0</v>
-      </c>
-      <c r="W16" s="28"/>
-      <c r="X16" s="13"/>
-      <c r="Y16" s="13"/>
-      <c r="Z16" s="13"/>
-      <c r="AA16" s="13"/>
-      <c r="AB16" s="13"/>
-      <c r="AC16" s="13"/>
-    </row>
-    <row r="17" spans="1:29" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="11">
+      <c r="P16" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="27">
+        <v>0</v>
+      </c>
+      <c r="R16" s="27">
+        <v>0</v>
+      </c>
+      <c r="S16" s="27">
+        <v>0</v>
+      </c>
+      <c r="T16" s="13">
+        <v>0</v>
+      </c>
+      <c r="U16" s="27">
+        <v>0</v>
+      </c>
+      <c r="V16" s="12">
+        <v>0</v>
+      </c>
+      <c r="W16" s="12">
+        <v>0</v>
+      </c>
+      <c r="X16" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="28">
         <v>1013673759</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="11" t="s">
         <v>30</v>
       </c>
       <c r="C17" s="4">
@@ -1863,58 +2194,81 @@
       <c r="D17" s="5">
         <v>124547.49999999999</v>
       </c>
-      <c r="E17" s="13">
-        <v>0</v>
-      </c>
-      <c r="F17" s="13">
+      <c r="E17" s="12">
+        <v>0</v>
+      </c>
+      <c r="F17" s="12">
         <v>140072.4</v>
       </c>
-      <c r="G17" s="13">
-        <v>0</v>
-      </c>
-      <c r="H17" s="21"/>
-      <c r="I17" s="23"/>
-      <c r="J17" s="25">
+      <c r="G17" s="12">
+        <v>0</v>
+      </c>
+      <c r="H17" s="20"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="24">
         <v>859927.6</v>
       </c>
-      <c r="K17" s="13">
+      <c r="K17" s="12">
         <v>519510</v>
       </c>
-      <c r="L17" s="13">
+      <c r="L17" s="12">
         <v>35000</v>
       </c>
-      <c r="M17" s="13">
+      <c r="M17" s="12">
         <v>100000</v>
       </c>
-      <c r="N17" s="27" t="s">
+      <c r="N17" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="O17" s="14">
+      <c r="O17" s="13">
         <f t="shared" si="0"/>
         <v>384510</v>
       </c>
-      <c r="P17" s="14"/>
-      <c r="Q17" s="28"/>
-      <c r="R17" s="28"/>
-      <c r="S17" s="28"/>
-      <c r="T17" s="14"/>
-      <c r="U17" s="28"/>
-      <c r="V17" s="13">
-        <v>0</v>
-      </c>
-      <c r="W17" s="28"/>
-      <c r="X17" s="13"/>
-      <c r="Y17" s="13"/>
-      <c r="Z17" s="13"/>
-      <c r="AA17" s="13"/>
-      <c r="AB17" s="13"/>
-      <c r="AC17" s="13"/>
-    </row>
-    <row r="18" spans="1:29" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="11">
+      <c r="P17" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="R17" s="27">
+        <v>0</v>
+      </c>
+      <c r="S17" s="27">
+        <v>0</v>
+      </c>
+      <c r="T17" s="13">
+        <v>0</v>
+      </c>
+      <c r="U17" s="27">
+        <v>0</v>
+      </c>
+      <c r="V17" s="12">
+        <v>0</v>
+      </c>
+      <c r="W17" s="12">
+        <v>0</v>
+      </c>
+      <c r="X17" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="28">
         <v>1003483344</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="11" t="s">
         <v>31</v>
       </c>
       <c r="C18" s="4">
@@ -1923,85 +2277,134 @@
       <c r="D18" s="5">
         <v>124547.49999999999</v>
       </c>
-      <c r="E18" s="13">
+      <c r="E18" s="12">
         <v>314406</v>
       </c>
-      <c r="F18" s="13">
+      <c r="F18" s="12">
         <v>140072.4</v>
       </c>
-      <c r="G18" s="13">
-        <v>0</v>
-      </c>
-      <c r="H18" s="21">
+      <c r="G18" s="12">
+        <v>0</v>
+      </c>
+      <c r="H18" s="20">
         <v>56000</v>
       </c>
-      <c r="I18" s="23" t="s">
+      <c r="I18" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="J18" s="25">
+      <c r="J18" s="24">
         <v>1118333.6000000001</v>
       </c>
-      <c r="K18" s="13">
-        <v>0</v>
-      </c>
-      <c r="L18" s="13">
-        <v>0</v>
-      </c>
-      <c r="M18" s="13">
-        <v>0</v>
-      </c>
-      <c r="N18" s="27"/>
-      <c r="O18" s="14">
+      <c r="K18" s="12">
+        <v>0</v>
+      </c>
+      <c r="L18" s="12">
+        <v>0</v>
+      </c>
+      <c r="M18" s="12">
+        <v>0</v>
+      </c>
+      <c r="N18" s="26"/>
+      <c r="O18" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P18" s="14"/>
-      <c r="Q18" s="28"/>
-      <c r="R18" s="28"/>
-      <c r="S18" s="28"/>
-      <c r="T18" s="14"/>
-      <c r="U18" s="28"/>
-      <c r="V18" s="13">
-        <v>0</v>
-      </c>
-      <c r="W18" s="28"/>
-      <c r="X18" s="13"/>
-      <c r="Y18" s="13"/>
-      <c r="Z18" s="13"/>
-      <c r="AA18" s="13"/>
-      <c r="AB18" s="13"/>
-      <c r="AC18" s="13"/>
-    </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A19" s="11"/>
-      <c r="B19" s="12"/>
+      <c r="P18" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="27">
+        <v>0</v>
+      </c>
+      <c r="R18" s="27">
+        <v>0</v>
+      </c>
+      <c r="S18" s="27">
+        <v>0</v>
+      </c>
+      <c r="T18" s="13">
+        <v>0</v>
+      </c>
+      <c r="U18" s="27">
+        <v>0</v>
+      </c>
+      <c r="V18" s="12">
+        <v>0</v>
+      </c>
+      <c r="W18" s="12">
+        <v>0</v>
+      </c>
+      <c r="X18" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A19" s="28"/>
+      <c r="B19" s="11"/>
       <c r="C19" s="4"/>
       <c r="D19" s="5"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
       <c r="I19" s="3"/>
-      <c r="J19" s="13"/>
-      <c r="K19" s="13"/>
-      <c r="L19" s="13"/>
-      <c r="M19" s="15"/>
-      <c r="N19" s="15"/>
-      <c r="O19" s="15"/>
-      <c r="P19" s="15"/>
-      <c r="Q19" s="28"/>
-      <c r="R19" s="28"/>
-      <c r="S19" s="28"/>
-      <c r="T19" s="15"/>
-      <c r="U19" s="28"/>
-      <c r="V19" s="13"/>
-      <c r="W19" s="28"/>
-      <c r="X19" s="13"/>
-      <c r="Y19" s="13"/>
-      <c r="Z19" s="13"/>
-      <c r="AA19" s="13"/>
-      <c r="AB19" s="13"/>
-      <c r="AC19" s="13"/>
+      <c r="J19" s="12"/>
+      <c r="K19" s="12"/>
+      <c r="L19" s="12"/>
+      <c r="M19" s="14"/>
+      <c r="N19" s="14"/>
+      <c r="O19" s="14"/>
+      <c r="P19" s="14"/>
+      <c r="Q19" s="27"/>
+      <c r="R19" s="27"/>
+      <c r="S19" s="27"/>
+      <c r="T19" s="14"/>
+      <c r="U19" s="27"/>
+      <c r="V19" s="12"/>
+      <c r="W19" s="12"/>
+      <c r="X19" s="12"/>
+      <c r="Y19" s="12"/>
+      <c r="Z19" s="12"/>
+      <c r="AA19" s="12"/>
+      <c r="AB19" s="27"/>
+    </row>
+    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="B24" s="15"/>
+    </row>
+    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="B25" s="15"/>
+    </row>
+    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="B26" s="15"/>
+    </row>
+    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="B27" s="15"/>
+    </row>
+    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="B28" s="15"/>
+    </row>
+    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="B29" s="15"/>
+    </row>
+    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="B30" s="15"/>
+    </row>
+    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="B31" s="15"/>
+    </row>
+    <row r="32" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="B32" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/empleados.xlsx
+++ b/empleados.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\NOMINA Y RRHH\NOMINA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Dropbox\NOMINA Y RRHH\NOMINA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{006309C9-E99C-4CAA-9656-3C882872B816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9171712A-D45C-4FC8-A78C-72B61E86E656}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DA975529-9E83-4FFA-BD35-5CA808A15280}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{DA975529-9E83-4FFA-BD35-5CA808A15280}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -20,23 +20,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <si>
     <t>CEDULA</t>
   </si>
@@ -134,63 +123,6 @@
     <t>MICHEL STEVEN HERNANDEZ ROJAS</t>
   </si>
   <si>
-    <t>360,000 vales</t>
-  </si>
-  <si>
-    <t>29,871 exedente vales</t>
-  </si>
-  <si>
-    <t>9 Dias incap</t>
-  </si>
-  <si>
-    <t>Vacaciones+250,000 Prestamo</t>
-  </si>
-  <si>
-    <t>35,000 (5) Caritas+18,000 sugeridos+300,000 Bono</t>
-  </si>
-  <si>
-    <t>7,000 (1) Carita</t>
-  </si>
-  <si>
-    <t>3 Dias incap</t>
-  </si>
-  <si>
-    <t>203,400 Prestamo+42,000 (6) Caritas</t>
-  </si>
-  <si>
-    <t>175,166 Prestamo+28,000 (4) caritas+30,000 sugeridos</t>
-  </si>
-  <si>
-    <t>1 Dia Incp+49,000 (7) Caritas+10,000 1 dia dotacion</t>
-  </si>
-  <si>
-    <t>56,000 (8) Caritas</t>
-  </si>
-  <si>
-    <t>276,350 Prestamo+56,000 (8) Caritas+10,000 sugeridos+292,161 VALES</t>
-  </si>
-  <si>
-    <t>56,000 (8) CARITAS+14,000 sugeridos+77,000 CAJA + 475,654 VALES</t>
-  </si>
-  <si>
-    <t>200,000 vales+70,000 (10) Caritas + 116,726 2 dias+30,000 3 dias dotacion+12,000 sugeridos</t>
-  </si>
-  <si>
-    <t>35,000 (5) caritas+10,000 1 dia dotacion+20,000 sugeridos+4,441 Utilidades+578,460 VALES</t>
-  </si>
-  <si>
-    <t>28,000 (4) Caritas+ 116,726 2 DIAS+18,000 Sugeridos+16,807 Utilidades+301,524 VALES</t>
-  </si>
-  <si>
-    <t>Se pagan los 3 dias de aux transporte</t>
-  </si>
-  <si>
-    <t>335,324 VALES</t>
-  </si>
-  <si>
-    <t>100,000 VALES+35,000 (5) Caritas</t>
-  </si>
-  <si>
     <t>VENTAS TOTALES</t>
   </si>
   <si>
@@ -231,6 +163,45 @@
   </si>
   <si>
     <t>0.14</t>
+  </si>
+  <si>
+    <t>CARLOS GUADALUPE JIMENEZ FLORIDO</t>
+  </si>
+  <si>
+    <t>500,000 vales</t>
+  </si>
+  <si>
+    <t>35,300 COOSERPARK+272,100 PRESTAMO+109,384 VALES</t>
+  </si>
+  <si>
+    <t>44,700 COOSERPARK+200,000 VALES</t>
+  </si>
+  <si>
+    <t>2 DIAS INCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44,700 COOSERPARK + 1 DIA LCNR </t>
+  </si>
+  <si>
+    <t>35,300 COOSERPARK+PLAN DE DATOS SEP-OCT+63,179 VALES</t>
+  </si>
+  <si>
+    <t>4 DIAS INCP DEVOLVER 33,213 EF</t>
+  </si>
+  <si>
+    <t>1 DIA LCNR+172,333 PRESTAMO+43,176 VALES</t>
+  </si>
+  <si>
+    <t>100,000 VALES</t>
+  </si>
+  <si>
+    <t>1 DIA INCP+141,141 VALES</t>
+  </si>
+  <si>
+    <t>DESCUENTO MEDIA DIA 13 OCT</t>
+  </si>
+  <si>
+    <t>INIC 15 OCT</t>
   </si>
 </sst>
 </file>
@@ -797,7 +768,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E263F044-EB2C-4A38-BF1B-A61CE6B829F6}">
-  <dimension ref="A1:AB32"/>
+  <dimension ref="A1:AB33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.140625" style="15" customWidth="1"/>
@@ -877,43 +848,43 @@
         <v>12</v>
       </c>
       <c r="P1" s="9" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="Q1" s="9" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="R1" s="9" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="S1" s="9" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="T1" s="9" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="U1" s="9" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="V1" s="8" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="W1" s="8" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="X1" s="8" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="Y1" s="8" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="Z1" s="8" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="AA1" s="8" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="AB1" s="8" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
@@ -933,19 +904,19 @@
         <v>0</v>
       </c>
       <c r="F2" s="12">
-        <v>640000.00000000012</v>
+        <v>0</v>
       </c>
       <c r="G2" s="12">
         <v>0</v>
       </c>
       <c r="H2" s="20">
-        <v>360000</v>
+        <v>500000</v>
       </c>
       <c r="I2" s="21" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J2" s="23">
-        <v>3000000.0000000005</v>
+        <v>3500000.0000000005</v>
       </c>
       <c r="K2" s="12">
         <v>0</v>
@@ -1001,7 +972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:28" ht="27" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A3" s="28">
         <v>94288721</v>
       </c>
@@ -1018,34 +989,33 @@
         <v>0</v>
       </c>
       <c r="F3" s="12">
-        <v>140072.4</v>
+        <v>0</v>
       </c>
       <c r="G3" s="12">
-        <v>700000</v>
+        <v>0</v>
       </c>
       <c r="H3" s="20">
-        <v>29871</v>
+        <f>381484+35300</f>
+        <v>416784</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="J3" s="24">
-        <v>1530056.6</v>
+        <v>583216</v>
       </c>
       <c r="K3" s="12">
-        <v>634511</v>
+        <v>0</v>
       </c>
       <c r="L3" s="12">
-        <v>56000</v>
+        <v>0</v>
       </c>
       <c r="M3" s="12">
-        <v>578511</v>
-      </c>
-      <c r="N3" s="19" t="s">
-        <v>43</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N3" s="19"/>
       <c r="O3" s="13">
-        <f t="shared" ref="O3:O18" si="0">K3-L3-M3</f>
+        <f t="shared" ref="O3:O19" si="0">K3-L3-M3</f>
         <v>0</v>
       </c>
       <c r="P3" s="13">
@@ -1088,7 +1058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="27" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A4" s="28">
         <v>1001200622</v>
       </c>
@@ -1105,28 +1075,31 @@
         <v>0</v>
       </c>
       <c r="F4" s="12">
-        <v>140072.4</v>
+        <v>0</v>
       </c>
       <c r="G4" s="12">
-        <v>600000</v>
-      </c>
-      <c r="H4" s="20"/>
-      <c r="I4" s="21"/>
+        <v>0</v>
+      </c>
+      <c r="H4" s="20">
+        <f>200000+44700</f>
+        <v>244700</v>
+      </c>
+      <c r="I4" s="21" t="s">
+        <v>49</v>
+      </c>
       <c r="J4" s="24">
-        <v>1459927.6</v>
+        <v>755300</v>
       </c>
       <c r="K4" s="12">
-        <v>650000</v>
+        <v>0</v>
       </c>
       <c r="L4" s="12">
-        <v>56000</v>
+        <v>0</v>
       </c>
       <c r="M4" s="12">
-        <v>594000</v>
-      </c>
-      <c r="N4" s="25" t="s">
-        <v>44</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N4" s="25"/>
       <c r="O4" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1171,7 +1144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A5" s="28">
         <v>1001045472</v>
       </c>
@@ -1182,40 +1155,42 @@
         <v>875452.5</v>
       </c>
       <c r="D5" s="5">
-        <v>124547.49999999999</v>
+        <v>107941.16666666666</v>
       </c>
       <c r="E5" s="12">
         <v>0</v>
       </c>
       <c r="F5" s="12">
-        <v>140072.4</v>
+        <v>0</v>
       </c>
       <c r="G5" s="12">
-        <v>700000</v>
-      </c>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
+        <v>0</v>
+      </c>
+      <c r="H5" s="20">
+        <v>0</v>
+      </c>
+      <c r="I5" s="21" t="s">
+        <v>50</v>
+      </c>
       <c r="J5" s="24">
-        <v>1559927.6</v>
+        <v>983393.66666666663</v>
       </c>
       <c r="K5" s="12">
-        <v>777558</v>
+        <v>0</v>
       </c>
       <c r="L5" s="12">
-        <v>186726</v>
+        <v>0</v>
       </c>
       <c r="M5" s="12">
-        <v>242000</v>
-      </c>
-      <c r="N5" s="19" t="s">
-        <v>45</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N5" s="19"/>
       <c r="O5" s="13">
         <f t="shared" si="0"/>
-        <v>348832</v>
+        <v>0</v>
       </c>
       <c r="P5" s="13">
-        <v>123456789</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="27">
         <v>0</v>
@@ -1233,28 +1208,28 @@
         <v>0</v>
       </c>
       <c r="V5" s="12">
-        <v>1500000</v>
+        <v>0</v>
       </c>
       <c r="W5" s="12">
-        <v>123456789</v>
+        <v>0</v>
       </c>
       <c r="X5" s="12">
-        <v>1500000</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="12">
-        <v>123456789</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="12">
-        <v>1500000</v>
+        <v>0</v>
       </c>
       <c r="AA5" s="12">
-        <v>3000000</v>
+        <v>0</v>
       </c>
       <c r="AB5" s="27">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="27" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A6" s="28">
         <v>80875830</v>
       </c>
@@ -1265,39 +1240,37 @@
         <v>875452.5</v>
       </c>
       <c r="D6" s="5">
-        <v>49819</v>
+        <v>124547.49999999999</v>
       </c>
       <c r="E6" s="12">
         <v>0</v>
       </c>
       <c r="F6" s="12">
-        <v>135403.32</v>
+        <v>0</v>
       </c>
       <c r="G6" s="12">
-        <v>700000</v>
-      </c>
-      <c r="H6" s="20"/>
-      <c r="I6" s="21" t="s">
-        <v>34</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H6" s="20">
+        <v>0</v>
+      </c>
+      <c r="I6" s="21"/>
       <c r="J6" s="24">
-        <v>1489868.18</v>
+        <v>1000000</v>
       </c>
       <c r="K6" s="12">
-        <v>1589070</v>
+        <v>0</v>
       </c>
       <c r="L6" s="12">
-        <v>35000</v>
+        <v>0</v>
       </c>
       <c r="M6" s="12">
-        <v>612901</v>
-      </c>
-      <c r="N6" s="19" t="s">
-        <v>46</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N6" s="19"/>
       <c r="O6" s="13">
         <f t="shared" si="0"/>
-        <v>941169</v>
+        <v>0</v>
       </c>
       <c r="P6" s="13">
         <v>0</v>
@@ -1347,28 +1320,28 @@
         <v>18</v>
       </c>
       <c r="C7" s="4">
-        <v>875452.5</v>
+        <v>817089</v>
       </c>
       <c r="D7" s="5">
-        <v>58122.166666666664</v>
+        <v>116244.33333333333</v>
       </c>
       <c r="E7" s="12">
         <v>0</v>
       </c>
       <c r="F7" s="12">
-        <v>140072.4</v>
+        <v>0</v>
       </c>
       <c r="G7" s="12">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="H7" s="20">
-        <v>250000</v>
+        <v>44700</v>
       </c>
       <c r="I7" s="21" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="J7" s="24">
-        <v>643502.2666666666</v>
+        <v>888633.33333333337</v>
       </c>
       <c r="K7" s="12">
         <v>0</v>
@@ -1381,7 +1354,6 @@
       </c>
       <c r="N7" s="26"/>
       <c r="O7" s="13">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="P7" s="13">
@@ -1424,7 +1396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="27" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A8" s="28">
         <v>1193092448</v>
       </c>
@@ -1441,49 +1413,51 @@
         <v>0</v>
       </c>
       <c r="F8" s="12">
-        <v>140072.4</v>
+        <v>0</v>
       </c>
       <c r="G8" s="12">
-        <v>700000</v>
-      </c>
-      <c r="H8" s="20"/>
-      <c r="I8" s="21"/>
+        <v>0</v>
+      </c>
+      <c r="H8" s="20">
+        <f>132769+35300</f>
+        <v>168069</v>
+      </c>
+      <c r="I8" s="21" t="s">
+        <v>52</v>
+      </c>
       <c r="J8" s="24">
-        <v>1559927.6</v>
+        <v>831931</v>
       </c>
       <c r="K8" s="12">
-        <v>550000</v>
+        <v>0</v>
       </c>
       <c r="L8" s="12">
-        <v>144726</v>
+        <v>0</v>
       </c>
       <c r="M8" s="12">
-        <v>336331</v>
-      </c>
-      <c r="N8" s="25" t="s">
-        <v>47</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N8" s="25"/>
       <c r="O8" s="13">
-        <f t="shared" si="0"/>
-        <v>68943</v>
+        <v>0</v>
       </c>
       <c r="P8" s="13">
-        <v>90000000</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="27">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="R8" s="27">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="S8" s="27">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T8" s="13">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="U8" s="27">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="V8" s="12">
         <v>0</v>
@@ -1501,10 +1475,10 @@
         <v>0</v>
       </c>
       <c r="AA8" s="12">
-        <v>3000000</v>
+        <v>0</v>
       </c>
       <c r="AB8" s="27">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
@@ -1524,22 +1498,20 @@
         <v>0</v>
       </c>
       <c r="F9" s="12">
-        <v>140072.4</v>
+        <v>0</v>
       </c>
       <c r="G9" s="12">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="H9" s="20">
-        <v>353000</v>
-      </c>
-      <c r="I9" s="21" t="s">
-        <v>36</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I9" s="21"/>
       <c r="J9" s="24">
-        <v>806927.6</v>
+        <v>1000000</v>
       </c>
       <c r="K9" s="12">
-        <v>-300000</v>
+        <v>0</v>
       </c>
       <c r="L9" s="12">
         <v>0</v>
@@ -1550,7 +1522,7 @@
       <c r="N9" s="19"/>
       <c r="O9" s="13">
         <f t="shared" si="0"/>
-        <v>-300000</v>
+        <v>0</v>
       </c>
       <c r="P9" s="13">
         <v>0</v>
@@ -1609,15 +1581,17 @@
         <v>0</v>
       </c>
       <c r="F10" s="12">
-        <v>172000</v>
+        <v>0</v>
       </c>
       <c r="G10" s="12">
-        <v>850000</v>
-      </c>
-      <c r="H10" s="20"/>
+        <v>0</v>
+      </c>
+      <c r="H10" s="20">
+        <v>0</v>
+      </c>
       <c r="I10" s="21"/>
       <c r="J10" s="24">
-        <v>1877547.5</v>
+        <v>1199547.5</v>
       </c>
       <c r="K10" s="12">
         <v>0</v>
@@ -1681,7 +1655,7 @@
         <v>22</v>
       </c>
       <c r="C11" s="4">
-        <v>7150000</v>
+        <v>0</v>
       </c>
       <c r="D11" s="5">
         <v>0</v>
@@ -1690,18 +1664,20 @@
         <v>0</v>
       </c>
       <c r="F11" s="12">
-        <v>572000</v>
+        <v>0</v>
       </c>
       <c r="G11" s="12">
-        <v>2000000</v>
-      </c>
-      <c r="H11" s="20"/>
+        <v>0</v>
+      </c>
+      <c r="H11" s="20">
+        <v>0</v>
+      </c>
       <c r="I11" s="21"/>
       <c r="J11" s="24">
-        <v>8578000</v>
+        <v>0</v>
       </c>
       <c r="K11" s="12">
-        <v>572000</v>
+        <v>0</v>
       </c>
       <c r="L11" s="12">
         <v>0</v>
@@ -1712,7 +1688,7 @@
       <c r="N11" s="26"/>
       <c r="O11" s="13">
         <f t="shared" si="0"/>
-        <v>572000</v>
+        <v>0</v>
       </c>
       <c r="P11" s="13">
         <v>0</v>
@@ -1771,19 +1747,17 @@
         <v>0</v>
       </c>
       <c r="F12" s="12">
-        <v>140072.4</v>
+        <v>0</v>
       </c>
       <c r="G12" s="12">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="H12" s="20">
-        <v>7000</v>
-      </c>
-      <c r="I12" s="21" t="s">
-        <v>37</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I12" s="21"/>
       <c r="J12" s="24">
-        <v>952927.6</v>
+        <v>1000000</v>
       </c>
       <c r="K12" s="12">
         <v>0</v>
@@ -1850,23 +1824,25 @@
         <v>1100000</v>
       </c>
       <c r="D13" s="5">
-        <v>99638</v>
+        <v>91334.833333333328</v>
       </c>
       <c r="E13" s="12">
         <v>0</v>
       </c>
       <c r="F13" s="12">
-        <v>146666.66666666666</v>
+        <v>0</v>
       </c>
       <c r="G13" s="12">
-        <v>600000</v>
-      </c>
-      <c r="H13" s="20"/>
+        <v>0</v>
+      </c>
+      <c r="H13" s="20">
+        <v>0</v>
+      </c>
       <c r="I13" s="21" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="J13" s="24">
-        <v>1652971.3333333333</v>
+        <v>1191334.8333333333</v>
       </c>
       <c r="K13" s="12">
         <v>0</v>
@@ -1877,9 +1853,7 @@
       <c r="M13" s="12">
         <v>0</v>
       </c>
-      <c r="N13" s="26" t="s">
-        <v>48</v>
-      </c>
+      <c r="N13" s="26"/>
       <c r="O13" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1938,22 +1912,20 @@
         <v>124547.49999999999</v>
       </c>
       <c r="E14" s="12">
-        <v>316367</v>
+        <v>0</v>
       </c>
       <c r="F14" s="12">
-        <v>140072.4</v>
+        <v>0</v>
       </c>
       <c r="G14" s="12">
         <v>0</v>
       </c>
       <c r="H14" s="20">
-        <v>245400</v>
-      </c>
-      <c r="I14" s="21" t="s">
-        <v>39</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I14" s="21"/>
       <c r="J14" s="24">
-        <v>930894.6</v>
+        <v>1000000</v>
       </c>
       <c r="K14" s="12">
         <v>0</v>
@@ -2017,41 +1989,39 @@
         <v>26</v>
       </c>
       <c r="C15" s="4">
-        <v>875452.5</v>
+        <v>817089</v>
       </c>
       <c r="D15" s="5">
-        <v>124547.49999999999</v>
+        <v>116244.33333333333</v>
       </c>
       <c r="E15" s="12">
-        <v>60861</v>
+        <v>0</v>
       </c>
       <c r="F15" s="12">
-        <v>135403.32</v>
+        <v>0</v>
       </c>
       <c r="G15" s="12">
         <v>0</v>
       </c>
       <c r="H15" s="20">
-        <v>233166</v>
+        <v>215509</v>
       </c>
       <c r="I15" s="21" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="J15" s="24">
-        <v>692291.67999999993</v>
+        <v>717824.33333333337</v>
       </c>
       <c r="K15" s="12">
-        <v>335324</v>
+        <v>0</v>
       </c>
       <c r="L15" s="12">
         <v>0</v>
       </c>
       <c r="M15" s="12">
-        <v>335324</v>
-      </c>
-      <c r="N15" s="26" t="s">
-        <v>49</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N15" s="26"/>
       <c r="O15" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2107,25 +2077,25 @@
         <v>875452.5</v>
       </c>
       <c r="D16" s="5">
-        <v>116244.33333333333</v>
+        <v>124547.49999999999</v>
       </c>
       <c r="E16" s="12">
-        <v>280770</v>
+        <v>0</v>
       </c>
       <c r="F16" s="12">
-        <v>135403.32</v>
+        <v>0</v>
       </c>
       <c r="G16" s="12">
         <v>0</v>
       </c>
       <c r="H16" s="20">
-        <v>59000</v>
+        <v>100000</v>
       </c>
       <c r="I16" s="22" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="J16" s="24">
-        <v>1078063.5133333334</v>
+        <v>900000</v>
       </c>
       <c r="K16" s="12">
         <v>0</v>
@@ -2192,43 +2162,45 @@
         <v>875452.5</v>
       </c>
       <c r="D17" s="5">
-        <v>124547.49999999999</v>
+        <v>116244.33333333333</v>
       </c>
       <c r="E17" s="12">
         <v>0</v>
       </c>
       <c r="F17" s="12">
-        <v>140072.4</v>
+        <v>0</v>
       </c>
       <c r="G17" s="12">
         <v>0</v>
       </c>
-      <c r="H17" s="20"/>
-      <c r="I17" s="22"/>
+      <c r="H17" s="20">
+        <v>141141</v>
+      </c>
+      <c r="I17" s="22" t="s">
+        <v>56</v>
+      </c>
       <c r="J17" s="24">
-        <v>859927.6</v>
+        <v>850555.83333333337</v>
       </c>
       <c r="K17" s="12">
-        <v>519510</v>
+        <v>0</v>
       </c>
       <c r="L17" s="12">
-        <v>35000</v>
+        <v>0</v>
       </c>
       <c r="M17" s="12">
-        <v>100000</v>
-      </c>
-      <c r="N17" s="26" t="s">
-        <v>50</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N17" s="26"/>
       <c r="O17" s="13">
         <f t="shared" si="0"/>
-        <v>384510</v>
+        <v>0</v>
       </c>
       <c r="P17" s="13">
         <v>0</v>
       </c>
       <c r="Q17" s="27" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="R17" s="27">
         <v>0</v>
@@ -2278,22 +2250,22 @@
         <v>124547.49999999999</v>
       </c>
       <c r="E18" s="12">
-        <v>314406</v>
+        <v>0</v>
       </c>
       <c r="F18" s="12">
-        <v>140072.4</v>
+        <v>0</v>
       </c>
       <c r="G18" s="12">
         <v>0</v>
       </c>
       <c r="H18" s="20">
-        <v>56000</v>
+        <v>29181</v>
       </c>
       <c r="I18" s="22" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="J18" s="24">
-        <v>1118333.6000000001</v>
+        <v>970819</v>
       </c>
       <c r="K18" s="12">
         <v>0</v>
@@ -2349,38 +2321,119 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A19" s="28"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="12"/>
-      <c r="K19" s="12"/>
-      <c r="L19" s="12"/>
-      <c r="M19" s="14"/>
-      <c r="N19" s="14"/>
-      <c r="O19" s="14"/>
-      <c r="P19" s="14"/>
-      <c r="Q19" s="27"/>
-      <c r="R19" s="27"/>
-      <c r="S19" s="27"/>
-      <c r="T19" s="14"/>
-      <c r="U19" s="27"/>
-      <c r="V19" s="12"/>
-      <c r="W19" s="12"/>
-      <c r="X19" s="12"/>
-      <c r="Y19" s="12"/>
-      <c r="Z19" s="12"/>
-      <c r="AA19" s="12"/>
-      <c r="AB19" s="27"/>
-    </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="B24" s="15"/>
+    <row r="19" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A19" s="28">
+        <v>1121959063</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="4">
+        <v>58363.5</v>
+      </c>
+      <c r="D19" s="5">
+        <v>8303.1666666666661</v>
+      </c>
+      <c r="E19" s="12">
+        <v>0</v>
+      </c>
+      <c r="F19" s="12">
+        <v>0</v>
+      </c>
+      <c r="G19" s="12">
+        <v>0</v>
+      </c>
+      <c r="H19" s="20">
+        <v>0</v>
+      </c>
+      <c r="I19" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="J19" s="24">
+        <v>66666.666666666672</v>
+      </c>
+      <c r="K19" s="12">
+        <v>0</v>
+      </c>
+      <c r="L19" s="12">
+        <v>0</v>
+      </c>
+      <c r="M19" s="12">
+        <v>0</v>
+      </c>
+      <c r="N19" s="26"/>
+      <c r="O19" s="13">
+        <v>0</v>
+      </c>
+      <c r="P19" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="27">
+        <v>0</v>
+      </c>
+      <c r="R19" s="27">
+        <v>0</v>
+      </c>
+      <c r="S19" s="27">
+        <v>0</v>
+      </c>
+      <c r="T19" s="13">
+        <v>0</v>
+      </c>
+      <c r="U19" s="27">
+        <v>0</v>
+      </c>
+      <c r="V19" s="12">
+        <v>0</v>
+      </c>
+      <c r="W19" s="12">
+        <v>0</v>
+      </c>
+      <c r="X19" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB19" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A20" s="28"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="12"/>
+      <c r="L20" s="12"/>
+      <c r="M20" s="14"/>
+      <c r="N20" s="14"/>
+      <c r="O20" s="14"/>
+      <c r="P20" s="14"/>
+      <c r="Q20" s="27"/>
+      <c r="R20" s="27"/>
+      <c r="S20" s="27"/>
+      <c r="T20" s="14"/>
+      <c r="U20" s="27"/>
+      <c r="V20" s="12"/>
+      <c r="W20" s="12"/>
+      <c r="X20" s="12"/>
+      <c r="Y20" s="12"/>
+      <c r="Z20" s="12"/>
+      <c r="AA20" s="12"/>
+      <c r="AB20" s="27"/>
     </row>
     <row r="25" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B25" s="15"/>
@@ -2405,6 +2458,9 @@
     </row>
     <row r="32" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B32" s="15"/>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B33" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
